--- a/Astro/predictions_dataset.xlsx
+++ b/Astro/predictions_dataset.xlsx
@@ -37,487 +37,487 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.02.202620</t>
-  </si>
-  <si>
-    <t>20.02.202621</t>
-  </si>
-  <si>
-    <t>20.02.202622</t>
-  </si>
-  <si>
-    <t>20.02.202623</t>
-  </si>
-  <si>
-    <t>21.02.20261</t>
-  </si>
-  <si>
-    <t>21.02.20262</t>
-  </si>
-  <si>
-    <t>21.02.20263</t>
-  </si>
-  <si>
-    <t>21.02.20264</t>
-  </si>
-  <si>
-    <t>21.02.20265</t>
-  </si>
-  <si>
-    <t>21.02.20266</t>
-  </si>
-  <si>
-    <t>21.02.20267</t>
-  </si>
-  <si>
-    <t>21.02.20268</t>
-  </si>
-  <si>
-    <t>21.02.20269</t>
-  </si>
-  <si>
-    <t>21.02.202610</t>
-  </si>
-  <si>
-    <t>21.02.202611</t>
-  </si>
-  <si>
-    <t>21.02.202612</t>
-  </si>
-  <si>
-    <t>21.02.202613</t>
-  </si>
-  <si>
-    <t>21.02.202614</t>
-  </si>
-  <si>
-    <t>21.02.202615</t>
-  </si>
-  <si>
-    <t>21.02.202616</t>
-  </si>
-  <si>
-    <t>21.02.202617</t>
-  </si>
-  <si>
-    <t>21.02.202618</t>
-  </si>
-  <si>
-    <t>21.02.202619</t>
-  </si>
-  <si>
-    <t>21.02.202620</t>
-  </si>
-  <si>
-    <t>21.02.202621</t>
-  </si>
-  <si>
-    <t>21.02.202622</t>
-  </si>
-  <si>
-    <t>21.02.202623</t>
-  </si>
-  <si>
-    <t>22.02.20261</t>
-  </si>
-  <si>
-    <t>22.02.20262</t>
-  </si>
-  <si>
-    <t>22.02.20263</t>
-  </si>
-  <si>
-    <t>22.02.20264</t>
-  </si>
-  <si>
-    <t>22.02.20265</t>
-  </si>
-  <si>
-    <t>22.02.20266</t>
-  </si>
-  <si>
-    <t>22.02.20267</t>
-  </si>
-  <si>
-    <t>22.02.20268</t>
-  </si>
-  <si>
-    <t>22.02.20269</t>
-  </si>
-  <si>
-    <t>22.02.202610</t>
-  </si>
-  <si>
-    <t>22.02.202611</t>
-  </si>
-  <si>
-    <t>22.02.202612</t>
-  </si>
-  <si>
-    <t>22.02.202613</t>
-  </si>
-  <si>
-    <t>22.02.202614</t>
-  </si>
-  <si>
-    <t>22.02.202615</t>
-  </si>
-  <si>
-    <t>22.02.202616</t>
-  </si>
-  <si>
-    <t>22.02.202617</t>
-  </si>
-  <si>
-    <t>22.02.202618</t>
-  </si>
-  <si>
-    <t>22.02.202619</t>
-  </si>
-  <si>
-    <t>22.02.202620</t>
-  </si>
-  <si>
-    <t>22.02.202621</t>
-  </si>
-  <si>
-    <t>22.02.202622</t>
-  </si>
-  <si>
-    <t>22.02.202623</t>
-  </si>
-  <si>
-    <t>23.02.20261</t>
-  </si>
-  <si>
-    <t>23.02.20262</t>
-  </si>
-  <si>
-    <t>23.02.20263</t>
-  </si>
-  <si>
-    <t>23.02.20264</t>
-  </si>
-  <si>
-    <t>23.02.20265</t>
-  </si>
-  <si>
-    <t>23.02.20266</t>
-  </si>
-  <si>
-    <t>23.02.20267</t>
-  </si>
-  <si>
-    <t>23.02.20268</t>
-  </si>
-  <si>
-    <t>23.02.20269</t>
-  </si>
-  <si>
-    <t>23.02.202610</t>
-  </si>
-  <si>
-    <t>23.02.202611</t>
-  </si>
-  <si>
-    <t>23.02.202612</t>
-  </si>
-  <si>
-    <t>23.02.202613</t>
-  </si>
-  <si>
-    <t>23.02.202614</t>
-  </si>
-  <si>
-    <t>23.02.202615</t>
-  </si>
-  <si>
-    <t>23.02.202616</t>
-  </si>
-  <si>
-    <t>23.02.202617</t>
-  </si>
-  <si>
-    <t>23.02.202618</t>
-  </si>
-  <si>
-    <t>23.02.202619</t>
-  </si>
-  <si>
-    <t>23.02.202620</t>
-  </si>
-  <si>
-    <t>23.02.202621</t>
-  </si>
-  <si>
-    <t>23.02.202622</t>
-  </si>
-  <si>
-    <t>23.02.202623</t>
-  </si>
-  <si>
-    <t>24.02.20261</t>
-  </si>
-  <si>
-    <t>24.02.20262</t>
-  </si>
-  <si>
-    <t>24.02.20263</t>
-  </si>
-  <si>
-    <t>24.02.20264</t>
-  </si>
-  <si>
-    <t>24.02.20265</t>
-  </si>
-  <si>
-    <t>24.02.20266</t>
-  </si>
-  <si>
-    <t>24.02.20267</t>
-  </si>
-  <si>
-    <t>24.02.20268</t>
-  </si>
-  <si>
-    <t>24.02.20269</t>
-  </si>
-  <si>
-    <t>24.02.202610</t>
-  </si>
-  <si>
-    <t>24.02.202611</t>
-  </si>
-  <si>
-    <t>24.02.202612</t>
-  </si>
-  <si>
-    <t>24.02.202613</t>
-  </si>
-  <si>
-    <t>24.02.202614</t>
-  </si>
-  <si>
-    <t>24.02.202615</t>
-  </si>
-  <si>
-    <t>24.02.202616</t>
-  </si>
-  <si>
-    <t>24.02.202617</t>
-  </si>
-  <si>
-    <t>24.02.202618</t>
-  </si>
-  <si>
-    <t>24.02.202619</t>
-  </si>
-  <si>
-    <t>24.02.202620</t>
-  </si>
-  <si>
-    <t>24.02.202621</t>
-  </si>
-  <si>
-    <t>24.02.202622</t>
-  </si>
-  <si>
-    <t>24.02.202623</t>
-  </si>
-  <si>
-    <t>25.02.20261</t>
-  </si>
-  <si>
-    <t>25.02.20262</t>
-  </si>
-  <si>
-    <t>25.02.20263</t>
-  </si>
-  <si>
-    <t>25.02.20264</t>
-  </si>
-  <si>
-    <t>25.02.20265</t>
-  </si>
-  <si>
-    <t>25.02.20266</t>
-  </si>
-  <si>
-    <t>25.02.20267</t>
-  </si>
-  <si>
-    <t>25.02.20268</t>
-  </si>
-  <si>
-    <t>25.02.20269</t>
-  </si>
-  <si>
-    <t>25.02.202610</t>
-  </si>
-  <si>
-    <t>25.02.202611</t>
-  </si>
-  <si>
-    <t>25.02.202612</t>
-  </si>
-  <si>
-    <t>25.02.202613</t>
-  </si>
-  <si>
-    <t>25.02.202614</t>
-  </si>
-  <si>
-    <t>25.02.202615</t>
-  </si>
-  <si>
-    <t>25.02.202616</t>
-  </si>
-  <si>
-    <t>25.02.202617</t>
-  </si>
-  <si>
-    <t>25.02.202618</t>
-  </si>
-  <si>
-    <t>25.02.202619</t>
-  </si>
-  <si>
-    <t>25.02.202620</t>
-  </si>
-  <si>
-    <t>25.02.202621</t>
-  </si>
-  <si>
-    <t>25.02.202622</t>
-  </si>
-  <si>
-    <t>25.02.202623</t>
-  </si>
-  <si>
-    <t>26.02.20261</t>
-  </si>
-  <si>
-    <t>26.02.20262</t>
-  </si>
-  <si>
-    <t>26.02.20263</t>
-  </si>
-  <si>
-    <t>26.02.20264</t>
-  </si>
-  <si>
-    <t>26.02.20265</t>
-  </si>
-  <si>
-    <t>26.02.20266</t>
-  </si>
-  <si>
-    <t>26.02.20267</t>
-  </si>
-  <si>
-    <t>26.02.20268</t>
-  </si>
-  <si>
-    <t>26.02.20269</t>
-  </si>
-  <si>
-    <t>26.02.202610</t>
-  </si>
-  <si>
-    <t>26.02.202611</t>
-  </si>
-  <si>
-    <t>26.02.202612</t>
-  </si>
-  <si>
-    <t>26.02.202613</t>
-  </si>
-  <si>
-    <t>26.02.202614</t>
-  </si>
-  <si>
-    <t>26.02.202615</t>
-  </si>
-  <si>
-    <t>26.02.202616</t>
-  </si>
-  <si>
-    <t>26.02.202617</t>
-  </si>
-  <si>
-    <t>26.02.202618</t>
-  </si>
-  <si>
-    <t>26.02.202619</t>
-  </si>
-  <si>
-    <t>26.02.202620</t>
-  </si>
-  <si>
-    <t>26.02.202621</t>
-  </si>
-  <si>
-    <t>26.02.202622</t>
-  </si>
-  <si>
-    <t>26.02.202623</t>
-  </si>
-  <si>
-    <t>27.02.20261</t>
-  </si>
-  <si>
-    <t>27.02.20262</t>
-  </si>
-  <si>
-    <t>27.02.20263</t>
-  </si>
-  <si>
-    <t>27.02.20264</t>
-  </si>
-  <si>
-    <t>27.02.20265</t>
-  </si>
-  <si>
-    <t>27.02.20266</t>
-  </si>
-  <si>
-    <t>27.02.20267</t>
-  </si>
-  <si>
-    <t>27.02.20268</t>
-  </si>
-  <si>
-    <t>27.02.20269</t>
-  </si>
-  <si>
-    <t>27.02.202610</t>
-  </si>
-  <si>
-    <t>27.02.202611</t>
-  </si>
-  <si>
-    <t>27.02.202612</t>
-  </si>
-  <si>
-    <t>27.02.202613</t>
-  </si>
-  <si>
-    <t>27.02.202614</t>
-  </si>
-  <si>
-    <t>27.02.202615</t>
-  </si>
-  <si>
-    <t>27.02.202616</t>
-  </si>
-  <si>
-    <t>27.02.202617</t>
-  </si>
-  <si>
-    <t>27.02.202618</t>
-  </si>
-  <si>
-    <t>27.02.202619</t>
+    <t>10.04.202610</t>
+  </si>
+  <si>
+    <t>10.04.202611</t>
+  </si>
+  <si>
+    <t>10.04.202612</t>
+  </si>
+  <si>
+    <t>10.04.202613</t>
+  </si>
+  <si>
+    <t>10.04.202614</t>
+  </si>
+  <si>
+    <t>10.04.202615</t>
+  </si>
+  <si>
+    <t>10.04.202616</t>
+  </si>
+  <si>
+    <t>10.04.202617</t>
+  </si>
+  <si>
+    <t>10.04.202618</t>
+  </si>
+  <si>
+    <t>10.04.202619</t>
+  </si>
+  <si>
+    <t>10.04.202620</t>
+  </si>
+  <si>
+    <t>10.04.202621</t>
+  </si>
+  <si>
+    <t>10.04.202622</t>
+  </si>
+  <si>
+    <t>10.04.202623</t>
+  </si>
+  <si>
+    <t>11.04.20261</t>
+  </si>
+  <si>
+    <t>11.04.20262</t>
+  </si>
+  <si>
+    <t>11.04.20263</t>
+  </si>
+  <si>
+    <t>11.04.20264</t>
+  </si>
+  <si>
+    <t>11.04.20265</t>
+  </si>
+  <si>
+    <t>11.04.20266</t>
+  </si>
+  <si>
+    <t>11.04.20267</t>
+  </si>
+  <si>
+    <t>11.04.20268</t>
+  </si>
+  <si>
+    <t>11.04.20269</t>
+  </si>
+  <si>
+    <t>11.04.202610</t>
+  </si>
+  <si>
+    <t>11.04.202611</t>
+  </si>
+  <si>
+    <t>11.04.202612</t>
+  </si>
+  <si>
+    <t>11.04.202613</t>
+  </si>
+  <si>
+    <t>11.04.202614</t>
+  </si>
+  <si>
+    <t>11.04.202615</t>
+  </si>
+  <si>
+    <t>11.04.202616</t>
+  </si>
+  <si>
+    <t>11.04.202617</t>
+  </si>
+  <si>
+    <t>11.04.202618</t>
+  </si>
+  <si>
+    <t>11.04.202619</t>
+  </si>
+  <si>
+    <t>11.04.202620</t>
+  </si>
+  <si>
+    <t>11.04.202621</t>
+  </si>
+  <si>
+    <t>11.04.202622</t>
+  </si>
+  <si>
+    <t>11.04.202623</t>
+  </si>
+  <si>
+    <t>12.04.20261</t>
+  </si>
+  <si>
+    <t>12.04.20262</t>
+  </si>
+  <si>
+    <t>12.04.20263</t>
+  </si>
+  <si>
+    <t>12.04.20264</t>
+  </si>
+  <si>
+    <t>12.04.20265</t>
+  </si>
+  <si>
+    <t>12.04.20266</t>
+  </si>
+  <si>
+    <t>12.04.20267</t>
+  </si>
+  <si>
+    <t>12.04.20268</t>
+  </si>
+  <si>
+    <t>12.04.20269</t>
+  </si>
+  <si>
+    <t>12.04.202610</t>
+  </si>
+  <si>
+    <t>12.04.202611</t>
+  </si>
+  <si>
+    <t>12.04.202612</t>
+  </si>
+  <si>
+    <t>12.04.202613</t>
+  </si>
+  <si>
+    <t>12.04.202614</t>
+  </si>
+  <si>
+    <t>12.04.202615</t>
+  </si>
+  <si>
+    <t>12.04.202616</t>
+  </si>
+  <si>
+    <t>12.04.202617</t>
+  </si>
+  <si>
+    <t>12.04.202618</t>
+  </si>
+  <si>
+    <t>12.04.202619</t>
+  </si>
+  <si>
+    <t>12.04.202620</t>
+  </si>
+  <si>
+    <t>12.04.202621</t>
+  </si>
+  <si>
+    <t>12.04.202622</t>
+  </si>
+  <si>
+    <t>12.04.202623</t>
+  </si>
+  <si>
+    <t>13.04.20261</t>
+  </si>
+  <si>
+    <t>13.04.20262</t>
+  </si>
+  <si>
+    <t>13.04.20263</t>
+  </si>
+  <si>
+    <t>13.04.20264</t>
+  </si>
+  <si>
+    <t>13.04.20265</t>
+  </si>
+  <si>
+    <t>13.04.20266</t>
+  </si>
+  <si>
+    <t>13.04.20267</t>
+  </si>
+  <si>
+    <t>13.04.20268</t>
+  </si>
+  <si>
+    <t>13.04.20269</t>
+  </si>
+  <si>
+    <t>13.04.202610</t>
+  </si>
+  <si>
+    <t>13.04.202611</t>
+  </si>
+  <si>
+    <t>13.04.202612</t>
+  </si>
+  <si>
+    <t>13.04.202613</t>
+  </si>
+  <si>
+    <t>13.04.202614</t>
+  </si>
+  <si>
+    <t>13.04.202615</t>
+  </si>
+  <si>
+    <t>13.04.202616</t>
+  </si>
+  <si>
+    <t>13.04.202617</t>
+  </si>
+  <si>
+    <t>13.04.202618</t>
+  </si>
+  <si>
+    <t>13.04.202619</t>
+  </si>
+  <si>
+    <t>13.04.202620</t>
+  </si>
+  <si>
+    <t>13.04.202621</t>
+  </si>
+  <si>
+    <t>13.04.202622</t>
+  </si>
+  <si>
+    <t>13.04.202623</t>
+  </si>
+  <si>
+    <t>14.04.20261</t>
+  </si>
+  <si>
+    <t>14.04.20262</t>
+  </si>
+  <si>
+    <t>14.04.20263</t>
+  </si>
+  <si>
+    <t>14.04.20264</t>
+  </si>
+  <si>
+    <t>14.04.20265</t>
+  </si>
+  <si>
+    <t>14.04.20266</t>
+  </si>
+  <si>
+    <t>14.04.20267</t>
+  </si>
+  <si>
+    <t>14.04.20268</t>
+  </si>
+  <si>
+    <t>14.04.20269</t>
+  </si>
+  <si>
+    <t>14.04.202610</t>
+  </si>
+  <si>
+    <t>14.04.202611</t>
+  </si>
+  <si>
+    <t>14.04.202612</t>
+  </si>
+  <si>
+    <t>14.04.202613</t>
+  </si>
+  <si>
+    <t>14.04.202614</t>
+  </si>
+  <si>
+    <t>14.04.202615</t>
+  </si>
+  <si>
+    <t>14.04.202616</t>
+  </si>
+  <si>
+    <t>14.04.202617</t>
+  </si>
+  <si>
+    <t>14.04.202618</t>
+  </si>
+  <si>
+    <t>14.04.202619</t>
+  </si>
+  <si>
+    <t>14.04.202620</t>
+  </si>
+  <si>
+    <t>14.04.202621</t>
+  </si>
+  <si>
+    <t>14.04.202622</t>
+  </si>
+  <si>
+    <t>14.04.202623</t>
+  </si>
+  <si>
+    <t>15.04.20261</t>
+  </si>
+  <si>
+    <t>15.04.20262</t>
+  </si>
+  <si>
+    <t>15.04.20263</t>
+  </si>
+  <si>
+    <t>15.04.20264</t>
+  </si>
+  <si>
+    <t>15.04.20265</t>
+  </si>
+  <si>
+    <t>15.04.20266</t>
+  </si>
+  <si>
+    <t>15.04.20267</t>
+  </si>
+  <si>
+    <t>15.04.20268</t>
+  </si>
+  <si>
+    <t>15.04.20269</t>
+  </si>
+  <si>
+    <t>15.04.202610</t>
+  </si>
+  <si>
+    <t>15.04.202611</t>
+  </si>
+  <si>
+    <t>15.04.202612</t>
+  </si>
+  <si>
+    <t>15.04.202613</t>
+  </si>
+  <si>
+    <t>15.04.202614</t>
+  </si>
+  <si>
+    <t>15.04.202615</t>
+  </si>
+  <si>
+    <t>15.04.202616</t>
+  </si>
+  <si>
+    <t>15.04.202617</t>
+  </si>
+  <si>
+    <t>15.04.202618</t>
+  </si>
+  <si>
+    <t>15.04.202619</t>
+  </si>
+  <si>
+    <t>15.04.202620</t>
+  </si>
+  <si>
+    <t>15.04.202621</t>
+  </si>
+  <si>
+    <t>15.04.202622</t>
+  </si>
+  <si>
+    <t>15.04.202623</t>
+  </si>
+  <si>
+    <t>16.04.20261</t>
+  </si>
+  <si>
+    <t>16.04.20262</t>
+  </si>
+  <si>
+    <t>16.04.20263</t>
+  </si>
+  <si>
+    <t>16.04.20264</t>
+  </si>
+  <si>
+    <t>16.04.20265</t>
+  </si>
+  <si>
+    <t>16.04.20266</t>
+  </si>
+  <si>
+    <t>16.04.20267</t>
+  </si>
+  <si>
+    <t>16.04.20268</t>
+  </si>
+  <si>
+    <t>16.04.20269</t>
+  </si>
+  <si>
+    <t>16.04.202610</t>
+  </si>
+  <si>
+    <t>16.04.202611</t>
+  </si>
+  <si>
+    <t>16.04.202612</t>
+  </si>
+  <si>
+    <t>16.04.202613</t>
+  </si>
+  <si>
+    <t>16.04.202614</t>
+  </si>
+  <si>
+    <t>16.04.202615</t>
+  </si>
+  <si>
+    <t>16.04.202616</t>
+  </si>
+  <si>
+    <t>16.04.202617</t>
+  </si>
+  <si>
+    <t>16.04.202618</t>
+  </si>
+  <si>
+    <t>16.04.202619</t>
+  </si>
+  <si>
+    <t>16.04.202620</t>
+  </si>
+  <si>
+    <t>16.04.202621</t>
+  </si>
+  <si>
+    <t>16.04.202622</t>
+  </si>
+  <si>
+    <t>16.04.202623</t>
+  </si>
+  <si>
+    <t>17.04.20261</t>
+  </si>
+  <si>
+    <t>17.04.20262</t>
+  </si>
+  <si>
+    <t>17.04.20263</t>
+  </si>
+  <si>
+    <t>17.04.20264</t>
+  </si>
+  <si>
+    <t>17.04.20265</t>
+  </si>
+  <si>
+    <t>17.04.20266</t>
+  </si>
+  <si>
+    <t>17.04.20267</t>
+  </si>
+  <si>
+    <t>17.04.20268</t>
+  </si>
+  <si>
+    <t>17.04.20269</t>
   </si>
 </sst>
 </file>
@@ -907,10 +907,10 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46073</v>
+        <v>46122</v>
       </c>
       <c r="B2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -924,10 +924,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46073</v>
+        <v>46122</v>
       </c>
       <c r="B3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -947,19 +947,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46073</v>
+        <v>46122</v>
       </c>
       <c r="B4">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>728</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>93.2</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -970,22 +970,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46073</v>
+        <v>46122</v>
       </c>
       <c r="B5">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>774</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>81.90000000000001</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>3.238</v>
       </c>
       <c r="G5" t="s">
         <v>9</v>
@@ -993,22 +993,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46073</v>
+        <v>46122</v>
       </c>
       <c r="B6">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>707</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>2.961</v>
       </c>
       <c r="G6" t="s">
         <v>10</v>
@@ -1016,269 +1016,269 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46074</v>
+        <v>46122</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>55.7</v>
+        <v>24</v>
+      </c>
+      <c r="F7">
+        <v>2.632</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46074</v>
+        <v>46122</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E8">
-        <v>55.8</v>
+        <v>29</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>2.421</v>
       </c>
       <c r="G8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46074</v>
+        <v>46122</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E9">
-        <v>56.4</v>
+        <v>31.6</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1.856</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46074</v>
+        <v>46122</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E10">
-        <v>57</v>
+        <v>31.8</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1.687</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46074</v>
+        <v>46122</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E11">
-        <v>57.6</v>
+        <v>29.4</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1.091</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46074</v>
+        <v>46122</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E12">
-        <v>58.2</v>
+        <v>30.2</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>0.438</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46074</v>
+        <v>46122</v>
       </c>
       <c r="B13">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E13">
-        <v>58.8</v>
+        <v>30.5</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46074</v>
+        <v>46122</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E14">
-        <v>59.9</v>
+        <v>29</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46074</v>
+        <v>46122</v>
       </c>
       <c r="B15">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E15">
-        <v>61.1</v>
+        <v>28.2</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46074</v>
+        <v>46122</v>
       </c>
       <c r="B16">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C16">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="E16">
-        <v>61.5</v>
+        <v>29.7</v>
       </c>
       <c r="F16">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46074</v>
+        <v>46123</v>
       </c>
       <c r="B17">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17">
-        <v>57.9</v>
-      </c>
-      <c r="F17">
-        <v>0.112</v>
-      </c>
-      <c r="G17" t="s">
-        <v>20</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46074</v>
+        <v>46123</v>
       </c>
       <c r="B18">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>58.2</v>
+        <v>25.1</v>
       </c>
       <c r="F18">
-        <v>0.416</v>
+        <v>0</v>
       </c>
       <c r="G18" t="s">
         <v>21</v>
@@ -1286,22 +1286,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46074</v>
+        <v>46123</v>
       </c>
       <c r="B19">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>2</v>
       </c>
       <c r="E19">
-        <v>59.3</v>
+        <v>25.1</v>
       </c>
       <c r="F19">
-        <v>0.736</v>
+        <v>0</v>
       </c>
       <c r="G19" t="s">
         <v>22</v>
@@ -1309,22 +1309,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46074</v>
+        <v>46123</v>
       </c>
       <c r="B20">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>60.8</v>
+        <v>25.1</v>
       </c>
       <c r="F20">
-        <v>0.845</v>
+        <v>0</v>
       </c>
       <c r="G20" t="s">
         <v>23</v>
@@ -1332,22 +1332,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46074</v>
+        <v>46123</v>
       </c>
       <c r="B21">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C21">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>64.5</v>
+        <v>27.4</v>
       </c>
       <c r="F21">
-        <v>0.823</v>
+        <v>0</v>
       </c>
       <c r="G21" t="s">
         <v>24</v>
@@ -1355,22 +1355,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46074</v>
+        <v>46123</v>
       </c>
       <c r="B22">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C22">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>68.2</v>
+        <v>31.2</v>
       </c>
       <c r="F22">
-        <v>0.792</v>
+        <v>0</v>
       </c>
       <c r="G22" t="s">
         <v>25</v>
@@ -1378,22 +1378,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46074</v>
+        <v>46123</v>
       </c>
       <c r="B23">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C23">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>70.09999999999999</v>
+        <v>34.2</v>
       </c>
       <c r="F23">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G23" t="s">
         <v>26</v>
@@ -1401,22 +1401,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46074</v>
+        <v>46123</v>
       </c>
       <c r="B24">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C24">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>71.8</v>
+        <v>35</v>
       </c>
       <c r="F24">
-        <v>0.248</v>
+        <v>0</v>
       </c>
       <c r="G24" t="s">
         <v>27</v>
@@ -1424,22 +1424,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46074</v>
+        <v>46123</v>
       </c>
       <c r="B25">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C25">
-        <v>10</v>
+        <v>169</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25">
-        <v>72</v>
+        <v>31.7</v>
       </c>
       <c r="F25">
-        <v>0.099</v>
+        <v>0.154</v>
       </c>
       <c r="G25" t="s">
         <v>28</v>
@@ -1447,22 +1447,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46074</v>
+        <v>46123</v>
       </c>
       <c r="B26">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E26">
-        <v>67.59999999999999</v>
+        <v>30.3</v>
       </c>
       <c r="F26">
-        <v>0.015</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G26" t="s">
         <v>29</v>
@@ -1470,22 +1470,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46074</v>
+        <v>46123</v>
       </c>
       <c r="B27">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E27">
-        <v>65.5</v>
+        <v>27.9</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>1.175</v>
       </c>
       <c r="G27" t="s">
         <v>30</v>
@@ -1493,22 +1493,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46074</v>
+        <v>46123</v>
       </c>
       <c r="B28">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E28">
-        <v>63.3</v>
+        <v>27.5</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>1.871</v>
       </c>
       <c r="G28" t="s">
         <v>31</v>
@@ -1516,22 +1516,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46074</v>
+        <v>46123</v>
       </c>
       <c r="B29">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E29">
-        <v>61.7</v>
+        <v>29.9</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>2.031</v>
       </c>
       <c r="G29" t="s">
         <v>32</v>
@@ -1539,22 +1539,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46074</v>
+        <v>46123</v>
       </c>
       <c r="B30">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>547</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E30">
-        <v>59.4</v>
+        <v>33.3</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="G30" t="s">
         <v>33</v>
@@ -1562,269 +1562,269 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46075</v>
+        <v>46123</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E31">
-        <v>57.6</v>
+        <v>35.9</v>
+      </c>
+      <c r="F31">
+        <v>2.062</v>
+      </c>
+      <c r="G31" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46075</v>
+        <v>46123</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>435</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E32">
-        <v>56.4</v>
+        <v>38.1</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>1.985</v>
       </c>
       <c r="G32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46075</v>
+        <v>46123</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E33">
-        <v>55.8</v>
+        <v>38.7</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1.934</v>
       </c>
       <c r="G33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46075</v>
+        <v>46123</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E34">
-        <v>54.5</v>
+        <v>35.4</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1.532</v>
       </c>
       <c r="G34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46075</v>
+        <v>46123</v>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E35">
-        <v>52</v>
+        <v>30.5</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>0.901</v>
       </c>
       <c r="G35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46075</v>
+        <v>46123</v>
       </c>
       <c r="B36">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E36">
-        <v>50.1</v>
+        <v>31.6</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>0.395</v>
       </c>
       <c r="G36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46075</v>
+        <v>46123</v>
       </c>
       <c r="B37">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E37">
-        <v>48.8</v>
+        <v>28.9</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="G37" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46075</v>
+        <v>46123</v>
       </c>
       <c r="B38">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E38">
-        <v>47.4</v>
+        <v>23.5</v>
       </c>
       <c r="F38">
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46075</v>
+        <v>46123</v>
       </c>
       <c r="B39">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C39">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39">
-        <v>46.1</v>
+        <v>21.1</v>
       </c>
       <c r="F39">
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46075</v>
+        <v>46123</v>
       </c>
       <c r="B40">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C40">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40">
-        <v>46.1</v>
+        <v>17.9</v>
       </c>
       <c r="F40">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46075</v>
+        <v>46124</v>
       </c>
       <c r="B41">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E41">
-        <v>40.5</v>
-      </c>
-      <c r="F41">
-        <v>0.139</v>
-      </c>
-      <c r="G41" t="s">
-        <v>43</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46075</v>
+        <v>46124</v>
       </c>
       <c r="B42">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42">
-        <v>35.3</v>
+        <v>7.7</v>
       </c>
       <c r="F42">
-        <v>0.472</v>
+        <v>0</v>
       </c>
       <c r="G42" t="s">
         <v>44</v>
@@ -1832,22 +1832,22 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46075</v>
+        <v>46124</v>
       </c>
       <c r="B43">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C43">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>2</v>
       </c>
       <c r="E43">
-        <v>32.5</v>
+        <v>2.4</v>
       </c>
       <c r="F43">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="G43" t="s">
         <v>45</v>
@@ -1855,22 +1855,22 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46075</v>
+        <v>46124</v>
       </c>
       <c r="B44">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C44">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="D44">
         <v>2</v>
       </c>
       <c r="E44">
-        <v>30.1</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>1.265</v>
+        <v>0</v>
       </c>
       <c r="G44" t="s">
         <v>46</v>
@@ -1878,22 +1878,22 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46075</v>
+        <v>46124</v>
       </c>
       <c r="B45">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C45">
-        <v>387</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45">
-        <v>27.7</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>1.466</v>
+        <v>0</v>
       </c>
       <c r="G45" t="s">
         <v>47</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46075</v>
+        <v>46124</v>
       </c>
       <c r="B46">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C46">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E46">
-        <v>30.6</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="G46" t="s">
         <v>48</v>
@@ -1924,22 +1924,22 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46075</v>
+        <v>46124</v>
       </c>
       <c r="B47">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C47">
-        <v>217</v>
+        <v>1</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E47">
-        <v>35.9</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>1.194</v>
+        <v>0</v>
       </c>
       <c r="G47" t="s">
         <v>49</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46075</v>
+        <v>46124</v>
       </c>
       <c r="B48">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C48">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48">
-        <v>42.3</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>0.741</v>
+        <v>0</v>
       </c>
       <c r="G48" t="s">
         <v>50</v>
@@ -1970,22 +1970,22 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46075</v>
+        <v>46124</v>
       </c>
       <c r="B49">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C49">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>0.252</v>
+        <v>0.19</v>
       </c>
       <c r="G49" t="s">
         <v>51</v>
@@ -1993,22 +1993,22 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46075</v>
+        <v>46124</v>
       </c>
       <c r="B50">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E50">
-        <v>47.4</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <v>0.033</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G50" t="s">
         <v>52</v>
@@ -2016,22 +2016,22 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46075</v>
+        <v>46124</v>
       </c>
       <c r="B51">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E51">
-        <v>50.1</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>1.932</v>
       </c>
       <c r="G51" t="s">
         <v>53</v>
@@ -2039,22 +2039,22 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46075</v>
+        <v>46124</v>
       </c>
       <c r="B52">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>713</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E52">
-        <v>49.4</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>2.694</v>
       </c>
       <c r="G52" t="s">
         <v>54</v>
@@ -2062,22 +2062,22 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46075</v>
+        <v>46124</v>
       </c>
       <c r="B53">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>788</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E53">
-        <v>50.7</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>3.077</v>
       </c>
       <c r="G53" t="s">
         <v>55</v>
@@ -2085,22 +2085,22 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46075</v>
+        <v>46124</v>
       </c>
       <c r="B54">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>811</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E54">
-        <v>54.5</v>
+        <v>0</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>3.132</v>
       </c>
       <c r="G54" t="s">
         <v>56</v>
@@ -2108,269 +2108,269 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46076</v>
+        <v>46124</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>777</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E55">
-        <v>57.6</v>
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>3.161</v>
+      </c>
+      <c r="G55" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46076</v>
+        <v>46124</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>689</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E56">
-        <v>58.2</v>
+        <v>0</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>3.048</v>
       </c>
       <c r="G56" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46076</v>
+        <v>46124</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>554</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E57">
-        <v>57.6</v>
+        <v>0</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>2.632</v>
       </c>
       <c r="G57" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46076</v>
+        <v>46124</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E58">
-        <v>58.8</v>
+        <v>0</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="G58" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46076</v>
+        <v>46124</v>
       </c>
       <c r="B59">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E59">
-        <v>60.5</v>
+        <v>0</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>1.471</v>
       </c>
       <c r="G59" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46076</v>
+        <v>46124</v>
       </c>
       <c r="B60">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E60">
-        <v>62.2</v>
+        <v>1.5</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>0.523</v>
       </c>
       <c r="G60" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46076</v>
+        <v>46124</v>
       </c>
       <c r="B61">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E61">
-        <v>62.8</v>
+        <v>2.4</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="G61" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46076</v>
+        <v>46124</v>
       </c>
       <c r="B62">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E62">
-        <v>62.8</v>
+        <v>2.4</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46076</v>
+        <v>46124</v>
       </c>
       <c r="B63">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C63">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E63">
-        <v>62.8</v>
+        <v>2.4</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46076</v>
+        <v>46124</v>
       </c>
       <c r="B64">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C64">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E64">
-        <v>67.7</v>
+        <v>1.5</v>
       </c>
       <c r="F64">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="B65">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C65">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E65">
-        <v>69.3</v>
-      </c>
-      <c r="F65">
-        <v>0.093</v>
-      </c>
-      <c r="G65" t="s">
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="B66">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C66">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E66">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F66">
-        <v>0.252</v>
+        <v>0</v>
       </c>
       <c r="G66" t="s">
         <v>67</v>
@@ -2378,22 +2378,22 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="B67">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E67">
-        <v>71.3</v>
+        <v>0</v>
       </c>
       <c r="F67">
-        <v>0.354</v>
+        <v>0</v>
       </c>
       <c r="G67" t="s">
         <v>68</v>
@@ -2401,22 +2401,22 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="B68">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C68">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E68">
-        <v>71.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="F68">
-        <v>0.411</v>
+        <v>0</v>
       </c>
       <c r="G68" t="s">
         <v>69</v>
@@ -2424,22 +2424,22 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="B69">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C69">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="D69">
         <v>3</v>
       </c>
       <c r="E69">
-        <v>72.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="F69">
-        <v>0.469</v>
+        <v>0</v>
       </c>
       <c r="G69" t="s">
         <v>70</v>
@@ -2447,22 +2447,22 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="B70">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C70">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="F70">
-        <v>0.425</v>
+        <v>0</v>
       </c>
       <c r="G70" t="s">
         <v>71</v>
@@ -2470,22 +2470,22 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="B71">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C71">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71">
-        <v>68.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="F71">
-        <v>0.347</v>
+        <v>0</v>
       </c>
       <c r="G71" t="s">
         <v>72</v>
@@ -2493,22 +2493,22 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="B72">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C72">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="D72">
         <v>3</v>
       </c>
       <c r="E72">
-        <v>70.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="F72">
-        <v>0.213</v>
+        <v>0</v>
       </c>
       <c r="G72" t="s">
         <v>73</v>
@@ -2516,22 +2516,22 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="B73">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C73">
-        <v>11</v>
+        <v>242</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E73">
-        <v>68.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="F73">
-        <v>0.126</v>
+        <v>0.179</v>
       </c>
       <c r="G73" t="s">
         <v>74</v>
@@ -2539,22 +2539,22 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="B74">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="D74">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E74">
-        <v>59.9</v>
+        <v>0</v>
       </c>
       <c r="F74">
-        <v>0.021</v>
+        <v>0.893</v>
       </c>
       <c r="G74" t="s">
         <v>75</v>
@@ -2562,22 +2562,22 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="B75">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>577</v>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E75">
-        <v>58.8</v>
+        <v>0</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>1.904</v>
       </c>
       <c r="G75" t="s">
         <v>76</v>
@@ -2585,22 +2585,22 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="B76">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>699</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E76">
-        <v>58.8</v>
+        <v>0</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>2.608</v>
       </c>
       <c r="G76" t="s">
         <v>77</v>
@@ -2608,22 +2608,22 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="B77">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>766</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E77">
-        <v>59.4</v>
+        <v>1.1</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>3.088</v>
       </c>
       <c r="G77" t="s">
         <v>78</v>
@@ -2631,22 +2631,22 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="B78">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>776</v>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E78">
-        <v>58.8</v>
+        <v>2.6</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>3.065</v>
       </c>
       <c r="G78" t="s">
         <v>79</v>
@@ -2654,269 +2654,269 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46077</v>
+        <v>46125</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>737</v>
       </c>
       <c r="D79">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E79">
-        <v>58.2</v>
+        <v>3.6</v>
+      </c>
+      <c r="F79">
+        <v>2.974</v>
+      </c>
+      <c r="G79" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46077</v>
+        <v>46125</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E80">
-        <v>59.4</v>
+        <v>5.2</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>2.902</v>
       </c>
       <c r="G80" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46077</v>
+        <v>46125</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="D81">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E81">
-        <v>60.5</v>
+        <v>8.4</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>2.393</v>
       </c>
       <c r="G81" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46077</v>
+        <v>46125</v>
       </c>
       <c r="B82">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E82">
-        <v>59.9</v>
+        <v>13.1</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>1.987</v>
       </c>
       <c r="G82" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46077</v>
+        <v>46125</v>
       </c>
       <c r="B83">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="D83">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E83">
-        <v>59.9</v>
+        <v>20.5</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>1.224</v>
       </c>
       <c r="G83" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46077</v>
+        <v>46125</v>
       </c>
       <c r="B84">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D84">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E84">
-        <v>59.9</v>
+        <v>32.3</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>0.457</v>
       </c>
       <c r="G84" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46077</v>
+        <v>46125</v>
       </c>
       <c r="B85">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E85">
-        <v>59.4</v>
+        <v>37.8</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="G85" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46077</v>
+        <v>46125</v>
       </c>
       <c r="B86">
+        <v>21</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
         <v>7</v>
       </c>
-      <c r="C86">
-        <v>0</v>
-      </c>
-      <c r="D86">
-        <v>4</v>
-      </c>
       <c r="E86">
-        <v>59.4</v>
+        <v>39.2</v>
       </c>
       <c r="F86">
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46077</v>
+        <v>46125</v>
       </c>
       <c r="B87">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C87">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E87">
-        <v>59.4</v>
+        <v>39.2</v>
       </c>
       <c r="F87">
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46077</v>
+        <v>46125</v>
       </c>
       <c r="B88">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C88">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D88">
         <v>6</v>
       </c>
       <c r="E88">
-        <v>60.3</v>
+        <v>39.2</v>
       </c>
       <c r="F88">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46077</v>
+        <v>46126</v>
       </c>
       <c r="B89">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C89">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E89">
-        <v>57.7</v>
-      </c>
-      <c r="F89">
-        <v>0.166</v>
-      </c>
-      <c r="G89" t="s">
-        <v>89</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46077</v>
+        <v>46126</v>
       </c>
       <c r="B90">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E90">
-        <v>55.3</v>
+        <v>28.2</v>
       </c>
       <c r="F90">
-        <v>0.482</v>
+        <v>0</v>
       </c>
       <c r="G90" t="s">
         <v>90</v>
@@ -2924,22 +2924,22 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46077</v>
+        <v>46126</v>
       </c>
       <c r="B91">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C91">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E91">
-        <v>57.1</v>
+        <v>25.9</v>
       </c>
       <c r="F91">
-        <v>0.709</v>
+        <v>0</v>
       </c>
       <c r="G91" t="s">
         <v>91</v>
@@ -2947,22 +2947,22 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46077</v>
+        <v>46126</v>
       </c>
       <c r="B92">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C92">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E92">
-        <v>59.1</v>
+        <v>26.7</v>
       </c>
       <c r="F92">
-        <v>0.6889999999999999</v>
+        <v>0</v>
       </c>
       <c r="G92" t="s">
         <v>92</v>
@@ -2970,22 +2970,22 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46077</v>
+        <v>46126</v>
       </c>
       <c r="B93">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C93">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E93">
-        <v>58.8</v>
+        <v>27.4</v>
       </c>
       <c r="F93">
-        <v>0.671</v>
+        <v>0</v>
       </c>
       <c r="G93" t="s">
         <v>93</v>
@@ -2993,22 +2993,22 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46077</v>
+        <v>46126</v>
       </c>
       <c r="B94">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C94">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E94">
-        <v>55.3</v>
+        <v>22.7</v>
       </c>
       <c r="F94">
-        <v>0.706</v>
+        <v>0</v>
       </c>
       <c r="G94" t="s">
         <v>94</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46077</v>
+        <v>46126</v>
       </c>
       <c r="B95">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C95">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="D95">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E95">
-        <v>48.6</v>
+        <v>21.9</v>
       </c>
       <c r="F95">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="G95" t="s">
         <v>95</v>
@@ -3039,22 +3039,22 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46077</v>
+        <v>46126</v>
       </c>
       <c r="B96">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C96">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="D96">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E96">
-        <v>45</v>
+        <v>25.8</v>
       </c>
       <c r="F96">
-        <v>0.5610000000000001</v>
+        <v>0</v>
       </c>
       <c r="G96" t="s">
         <v>96</v>
@@ -3062,22 +3062,22 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46077</v>
+        <v>46126</v>
       </c>
       <c r="B97">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C97">
-        <v>25</v>
+        <v>197</v>
       </c>
       <c r="D97">
         <v>6</v>
       </c>
       <c r="E97">
-        <v>41.7</v>
+        <v>17.9</v>
       </c>
       <c r="F97">
-        <v>0.255</v>
+        <v>0.179</v>
       </c>
       <c r="G97" t="s">
         <v>97</v>
@@ -3085,22 +3085,22 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46077</v>
+        <v>46126</v>
       </c>
       <c r="B98">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D98">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E98">
-        <v>31.6</v>
+        <v>16.1</v>
       </c>
       <c r="F98">
-        <v>0.046</v>
+        <v>0.773</v>
       </c>
       <c r="G98" t="s">
         <v>98</v>
@@ -3108,22 +3108,22 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46077</v>
+        <v>46126</v>
       </c>
       <c r="B99">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="D99">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E99">
-        <v>26.9</v>
+        <v>22.2</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>1.553</v>
       </c>
       <c r="G99" t="s">
         <v>99</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46077</v>
+        <v>46126</v>
       </c>
       <c r="B100">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="D100">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E100">
-        <v>24.5</v>
+        <v>29</v>
       </c>
       <c r="F100">
-        <v>0</v>
+        <v>1.885</v>
       </c>
       <c r="G100" t="s">
         <v>100</v>
@@ -3154,22 +3154,22 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46077</v>
+        <v>46126</v>
       </c>
       <c r="B101">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="D101">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E101">
-        <v>21.2</v>
+        <v>32.3</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>2.004</v>
       </c>
       <c r="G101" t="s">
         <v>101</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46077</v>
+        <v>46126</v>
       </c>
       <c r="B102">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>542</v>
       </c>
       <c r="D102">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E102">
-        <v>17.8</v>
+        <v>32.2</v>
       </c>
       <c r="F102">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="G102" t="s">
         <v>102</v>
@@ -3200,269 +3200,269 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46078</v>
+        <v>46126</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>536</v>
       </c>
       <c r="D103">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E103">
-        <v>16.1</v>
+        <v>30.3</v>
+      </c>
+      <c r="F103">
+        <v>2.016</v>
+      </c>
+      <c r="G103" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46078</v>
+        <v>46126</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>507</v>
       </c>
       <c r="D104">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E104">
-        <v>17.8</v>
+        <v>26</v>
       </c>
       <c r="F104">
-        <v>0</v>
+        <v>2.049</v>
       </c>
       <c r="G104" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46078</v>
+        <v>46126</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>436</v>
       </c>
       <c r="D105">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E105">
-        <v>18.7</v>
+        <v>21.8</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>1.994</v>
       </c>
       <c r="G105" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46078</v>
+        <v>46126</v>
       </c>
       <c r="B106">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="D106">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E106">
-        <v>17</v>
+        <v>19.6</v>
       </c>
       <c r="F106">
-        <v>0</v>
+        <v>1.825</v>
       </c>
       <c r="G106" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46078</v>
+        <v>46126</v>
       </c>
       <c r="B107">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="D107">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E107">
-        <v>17</v>
+        <v>20.9</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>1.135</v>
       </c>
       <c r="G107" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46078</v>
+        <v>46126</v>
       </c>
       <c r="B108">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E108">
-        <v>17</v>
+        <v>24.7</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="G108" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46078</v>
+        <v>46126</v>
       </c>
       <c r="B109">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C109">
         <v>0</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E109">
-        <v>15.3</v>
+        <v>23.5</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="G109" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46078</v>
+        <v>46126</v>
       </c>
       <c r="B110">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C110">
         <v>0</v>
       </c>
       <c r="D110">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E110">
-        <v>15.3</v>
+        <v>22.7</v>
       </c>
       <c r="F110">
         <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46078</v>
+        <v>46126</v>
       </c>
       <c r="B111">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C111">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E111">
-        <v>16.1</v>
+        <v>21.9</v>
       </c>
       <c r="F111">
         <v>0</v>
       </c>
       <c r="G111" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46078</v>
+        <v>46126</v>
       </c>
       <c r="B112">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C112">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E112">
-        <v>14.3</v>
+        <v>21.1</v>
       </c>
       <c r="F112">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="G112" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46078</v>
+        <v>46127</v>
       </c>
       <c r="B113">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E113">
-        <v>12.4</v>
-      </c>
-      <c r="F113">
-        <v>0.419</v>
-      </c>
-      <c r="G113" t="s">
-        <v>112</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46078</v>
+        <v>46127</v>
       </c>
       <c r="B114">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C114">
-        <v>391</v>
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E114">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="F114">
-        <v>1.085</v>
+        <v>0</v>
       </c>
       <c r="G114" t="s">
         <v>113</v>
@@ -3470,22 +3470,22 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46078</v>
+        <v>46127</v>
       </c>
       <c r="B115">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C115">
-        <v>482</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E115">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F115">
-        <v>1.733</v>
+        <v>0</v>
       </c>
       <c r="G115" t="s">
         <v>114</v>
@@ -3493,22 +3493,22 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46078</v>
+        <v>46127</v>
       </c>
       <c r="B116">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C116">
-        <v>534</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E116">
-        <v>6.8</v>
+        <v>2.4</v>
       </c>
       <c r="F116">
-        <v>2.334</v>
+        <v>0</v>
       </c>
       <c r="G116" t="s">
         <v>115</v>
@@ -3516,22 +3516,22 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46078</v>
+        <v>46127</v>
       </c>
       <c r="B117">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C117">
-        <v>529</v>
+        <v>0</v>
       </c>
       <c r="D117">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E117">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="F117">
-        <v>2.394</v>
+        <v>0</v>
       </c>
       <c r="G117" t="s">
         <v>116</v>
@@ -3539,22 +3539,22 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46078</v>
+        <v>46127</v>
       </c>
       <c r="B118">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C118">
-        <v>454</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E118">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="F118">
-        <v>2.472</v>
+        <v>0</v>
       </c>
       <c r="G118" t="s">
         <v>117</v>
@@ -3562,22 +3562,22 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46078</v>
+        <v>46127</v>
       </c>
       <c r="B119">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C119">
-        <v>320</v>
+        <v>2</v>
       </c>
       <c r="D119">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E119">
-        <v>9.6</v>
+        <v>2.4</v>
       </c>
       <c r="F119">
-        <v>2.069</v>
+        <v>0</v>
       </c>
       <c r="G119" t="s">
         <v>118</v>
@@ -3585,22 +3585,22 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46078</v>
+        <v>46127</v>
       </c>
       <c r="B120">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C120">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="D120">
         <v>6</v>
       </c>
       <c r="E120">
-        <v>17.3</v>
+        <v>2.3</v>
       </c>
       <c r="F120">
-        <v>1.426</v>
+        <v>0</v>
       </c>
       <c r="G120" t="s">
         <v>119</v>
@@ -3608,22 +3608,22 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46078</v>
+        <v>46127</v>
       </c>
       <c r="B121">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C121">
-        <v>36</v>
+        <v>244</v>
       </c>
       <c r="D121">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E121">
-        <v>25.9</v>
+        <v>1.6</v>
       </c>
       <c r="F121">
-        <v>0.548</v>
+        <v>0.228</v>
       </c>
       <c r="G121" t="s">
         <v>120</v>
@@ -3631,22 +3631,22 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46078</v>
+        <v>46127</v>
       </c>
       <c r="B122">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="D122">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E122">
-        <v>28.5</v>
+        <v>1.2</v>
       </c>
       <c r="F122">
-        <v>0.057</v>
+        <v>0.914</v>
       </c>
       <c r="G122" t="s">
         <v>121</v>
@@ -3654,22 +3654,22 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46078</v>
+        <v>46127</v>
       </c>
       <c r="B123">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>581</v>
       </c>
       <c r="D123">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E123">
-        <v>29.2</v>
+        <v>0.6</v>
       </c>
       <c r="F123">
-        <v>0</v>
+        <v>1.899</v>
       </c>
       <c r="G123" t="s">
         <v>122</v>
@@ -3677,22 +3677,22 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46078</v>
+        <v>46127</v>
       </c>
       <c r="B124">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>707</v>
       </c>
       <c r="D124">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E124">
-        <v>27.7</v>
+        <v>0</v>
       </c>
       <c r="F124">
-        <v>0</v>
+        <v>2.567</v>
       </c>
       <c r="G124" t="s">
         <v>123</v>
@@ -3700,22 +3700,22 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46078</v>
+        <v>46127</v>
       </c>
       <c r="B125">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>785</v>
       </c>
       <c r="D125">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E125">
-        <v>23.6</v>
+        <v>0</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>3.049</v>
       </c>
       <c r="G125" t="s">
         <v>124</v>
@@ -3723,22 +3723,22 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46078</v>
+        <v>46127</v>
       </c>
       <c r="B126">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>804</v>
       </c>
       <c r="D126">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E126">
-        <v>17.8</v>
+        <v>0.6</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="G126" t="s">
         <v>125</v>
@@ -3746,269 +3746,269 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46079</v>
+        <v>46127</v>
       </c>
       <c r="B127">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>768</v>
       </c>
       <c r="D127">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E127">
-        <v>15.3</v>
+        <v>1.1</v>
+      </c>
+      <c r="F127">
+        <v>3.203</v>
+      </c>
+      <c r="G127" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46079</v>
+        <v>46127</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>674</v>
       </c>
       <c r="D128">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E128">
-        <v>17</v>
+        <v>2.7</v>
       </c>
       <c r="F128">
-        <v>0</v>
+        <v>2.992</v>
       </c>
       <c r="G128" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46079</v>
+        <v>46127</v>
       </c>
       <c r="B129">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="D129">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E129">
-        <v>18.7</v>
+        <v>5.8</v>
       </c>
       <c r="F129">
-        <v>0</v>
+        <v>2.588</v>
       </c>
       <c r="G129" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46079</v>
+        <v>46127</v>
       </c>
       <c r="B130">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>361</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E130">
-        <v>20.3</v>
+        <v>10.3</v>
       </c>
       <c r="F130">
-        <v>0</v>
+        <v>2.107</v>
       </c>
       <c r="G130" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46079</v>
+        <v>46127</v>
       </c>
       <c r="B131">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="D131">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E131">
-        <v>20.3</v>
+        <v>13.1</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="G131" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46079</v>
+        <v>46127</v>
       </c>
       <c r="B132">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E132">
-        <v>19.5</v>
+        <v>12.6</v>
       </c>
       <c r="F132">
-        <v>0</v>
+        <v>0.496</v>
       </c>
       <c r="G132" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46079</v>
+        <v>46127</v>
       </c>
       <c r="B133">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C133">
         <v>0</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E133">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="G133" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46079</v>
+        <v>46127</v>
       </c>
       <c r="B134">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C134">
         <v>0</v>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E134">
-        <v>19.5</v>
+        <v>8.6</v>
       </c>
       <c r="F134">
         <v>0</v>
       </c>
       <c r="G134" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46079</v>
+        <v>46127</v>
       </c>
       <c r="B135">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C135">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D135">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E135">
-        <v>18.7</v>
+        <v>11.2</v>
       </c>
       <c r="F135">
         <v>0</v>
       </c>
       <c r="G135" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46079</v>
+        <v>46127</v>
       </c>
       <c r="B136">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C136">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="D136">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E136">
-        <v>15.6</v>
+        <v>14.6</v>
       </c>
       <c r="F136">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="G136" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46079</v>
+        <v>46128</v>
       </c>
       <c r="B137">
+        <v>0</v>
+      </c>
+      <c r="C137">
+        <v>0</v>
+      </c>
+      <c r="D137">
         <v>10</v>
       </c>
-      <c r="C137">
-        <v>263</v>
-      </c>
-      <c r="D137">
-        <v>4</v>
-      </c>
       <c r="E137">
-        <v>12.3</v>
-      </c>
-      <c r="F137">
-        <v>0.437</v>
-      </c>
-      <c r="G137" t="s">
-        <v>135</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46079</v>
+        <v>46128</v>
       </c>
       <c r="B138">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C138">
-        <v>386</v>
+        <v>0</v>
       </c>
       <c r="D138">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E138">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="F138">
-        <v>1.009</v>
+        <v>0</v>
       </c>
       <c r="G138" t="s">
         <v>136</v>
@@ -4016,22 +4016,22 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46079</v>
+        <v>46128</v>
       </c>
       <c r="B139">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C139">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="D139">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E139">
-        <v>9.5</v>
+        <v>5.1</v>
       </c>
       <c r="F139">
-        <v>1.787</v>
+        <v>0</v>
       </c>
       <c r="G139" t="s">
         <v>137</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46079</v>
+        <v>46128</v>
       </c>
       <c r="B140">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C140">
-        <v>524</v>
+        <v>0</v>
       </c>
       <c r="D140">
         <v>7</v>
       </c>
       <c r="E140">
-        <v>6.7</v>
+        <v>2.4</v>
       </c>
       <c r="F140">
-        <v>2.299</v>
+        <v>0</v>
       </c>
       <c r="G140" t="s">
         <v>138</v>
@@ -4062,22 +4062,22 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46079</v>
+        <v>46128</v>
       </c>
       <c r="B141">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C141">
-        <v>519</v>
+        <v>0</v>
       </c>
       <c r="D141">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E141">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="F141">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="G141" t="s">
         <v>139</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46079</v>
+        <v>46128</v>
       </c>
       <c r="B142">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C142">
-        <v>452</v>
+        <v>0</v>
       </c>
       <c r="D142">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E142">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="F142">
-        <v>2.351</v>
+        <v>0</v>
       </c>
       <c r="G142" t="s">
         <v>140</v>
@@ -4108,22 +4108,22 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46079</v>
+        <v>46128</v>
       </c>
       <c r="B143">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C143">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="D143">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E143">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="F143">
-        <v>2.074</v>
+        <v>0</v>
       </c>
       <c r="G143" t="s">
         <v>141</v>
@@ -4131,22 +4131,22 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46079</v>
+        <v>46128</v>
       </c>
       <c r="B144">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C144">
-        <v>186</v>
+        <v>84</v>
       </c>
       <c r="D144">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E144">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="F144">
-        <v>1.577</v>
+        <v>0</v>
       </c>
       <c r="G144" t="s">
         <v>142</v>
@@ -4154,22 +4154,22 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46079</v>
+        <v>46128</v>
       </c>
       <c r="B145">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C145">
-        <v>47</v>
+        <v>250</v>
       </c>
       <c r="D145">
         <v>8</v>
       </c>
       <c r="E145">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="F145">
-        <v>0.695</v>
+        <v>0.229</v>
       </c>
       <c r="G145" t="s">
         <v>143</v>
@@ -4177,22 +4177,22 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46079</v>
+        <v>46128</v>
       </c>
       <c r="B146">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="D146">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E146">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="F146">
-        <v>0.08</v>
+        <v>0.929</v>
       </c>
       <c r="G146" t="s">
         <v>144</v>
@@ -4200,22 +4200,22 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46079</v>
+        <v>46128</v>
       </c>
       <c r="B147">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>578</v>
       </c>
       <c r="D147">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E147">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>1.936</v>
       </c>
       <c r="G147" t="s">
         <v>145</v>
@@ -4223,22 +4223,22 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46079</v>
+        <v>46128</v>
       </c>
       <c r="B148">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>694</v>
       </c>
       <c r="D148">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="F148">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="G148" t="s">
         <v>146</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46079</v>
+        <v>46128</v>
       </c>
       <c r="B149">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>757</v>
       </c>
       <c r="D149">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>2.848</v>
       </c>
       <c r="G149" t="s">
         <v>147</v>
@@ -4269,22 +4269,22 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46079</v>
+        <v>46128</v>
       </c>
       <c r="B150">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>755</v>
       </c>
       <c r="D150">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="F150">
-        <v>0</v>
+        <v>2.995</v>
       </c>
       <c r="G150" t="s">
         <v>148</v>
@@ -4292,269 +4292,269 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46080</v>
+        <v>46128</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>706</v>
       </c>
       <c r="D151">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E151">
-        <v>2.8</v>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F151">
+        <v>2.965</v>
+      </c>
+      <c r="G151" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46080</v>
+        <v>46128</v>
       </c>
       <c r="B152">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>623</v>
       </c>
       <c r="D152">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E152">
-        <v>7.3</v>
+        <v>10.3</v>
       </c>
       <c r="F152">
-        <v>0</v>
+        <v>2.645</v>
       </c>
       <c r="G152" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46080</v>
+        <v>46128</v>
       </c>
       <c r="B153">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="D153">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E153">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>2.361</v>
       </c>
       <c r="G153" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46080</v>
+        <v>46128</v>
       </c>
       <c r="B154">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="D154">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E154">
-        <v>14.4</v>
+        <v>11.3</v>
       </c>
       <c r="F154">
-        <v>0</v>
+        <v>1.913</v>
       </c>
       <c r="G154" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46080</v>
+        <v>46128</v>
       </c>
       <c r="B155">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="D155">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E155">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>1.226</v>
       </c>
       <c r="G155" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46080</v>
+        <v>46128</v>
       </c>
       <c r="B156">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D156">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E156">
-        <v>24.5</v>
+        <v>15</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>0.499</v>
       </c>
       <c r="G156" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46080</v>
+        <v>46128</v>
       </c>
       <c r="B157">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C157">
         <v>0</v>
       </c>
       <c r="D157">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E157">
-        <v>27.7</v>
+        <v>14.6</v>
       </c>
       <c r="F157">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="G157" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46080</v>
+        <v>46128</v>
       </c>
       <c r="B158">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C158">
         <v>0</v>
       </c>
       <c r="D158">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E158">
-        <v>30.8</v>
+        <v>13.7</v>
       </c>
       <c r="F158">
         <v>0</v>
       </c>
       <c r="G158" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46080</v>
+        <v>46128</v>
       </c>
       <c r="B159">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C159">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D159">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E159">
-        <v>33.9</v>
+        <v>12</v>
       </c>
       <c r="F159">
         <v>0</v>
       </c>
       <c r="G159" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46080</v>
+        <v>46128</v>
       </c>
       <c r="B160">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C160">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D160">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E160">
-        <v>31</v>
+        <v>10.3</v>
       </c>
       <c r="F160">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="G160" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="B161">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C161">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="D161">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E161">
-        <v>25.7</v>
-      </c>
-      <c r="F161">
-        <v>0.349</v>
-      </c>
-      <c r="G161" t="s">
-        <v>158</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="B162">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C162">
-        <v>335</v>
+        <v>0</v>
       </c>
       <c r="D162">
+        <v>10</v>
+      </c>
+      <c r="E162">
         <v>6</v>
       </c>
-      <c r="E162">
-        <v>23.8</v>
-      </c>
       <c r="F162">
-        <v>0.844</v>
+        <v>0</v>
       </c>
       <c r="G162" t="s">
         <v>159</v>
@@ -4562,22 +4562,22 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="B163">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C163">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="D163">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E163">
-        <v>22.4</v>
+        <v>3.3</v>
       </c>
       <c r="F163">
-        <v>1.538</v>
+        <v>0</v>
       </c>
       <c r="G163" t="s">
         <v>160</v>
@@ -4585,22 +4585,22 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="B164">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C164">
-        <v>447</v>
+        <v>0</v>
       </c>
       <c r="D164">
         <v>8</v>
       </c>
       <c r="E164">
-        <v>20.6</v>
+        <v>6</v>
       </c>
       <c r="F164">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="G164" t="s">
         <v>161</v>
@@ -4608,22 +4608,22 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="B165">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C165">
-        <v>443</v>
+        <v>0</v>
       </c>
       <c r="D165">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E165">
-        <v>18.7</v>
+        <v>12.9</v>
       </c>
       <c r="F165">
-        <v>2.077</v>
+        <v>0</v>
       </c>
       <c r="G165" t="s">
         <v>162</v>
@@ -4631,22 +4631,22 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="B166">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C166">
-        <v>381</v>
+        <v>0</v>
       </c>
       <c r="D166">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E166">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="F166">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="G166" t="s">
         <v>163</v>
@@ -4654,22 +4654,22 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="B167">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C167">
-        <v>271</v>
+        <v>2</v>
       </c>
       <c r="D167">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E167">
-        <v>24.2</v>
+        <v>25.9</v>
       </c>
       <c r="F167">
-        <v>1.723</v>
+        <v>0</v>
       </c>
       <c r="G167" t="s">
         <v>164</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="B168">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C168">
-        <v>141</v>
+        <v>60</v>
       </c>
       <c r="D168">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E168">
-        <v>31.8</v>
+        <v>31.2</v>
       </c>
       <c r="F168">
-        <v>1.084</v>
+        <v>0</v>
       </c>
       <c r="G168" t="s">
         <v>165</v>
@@ -4700,22 +4700,22 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="B169">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C169">
-        <v>33</v>
+        <v>178</v>
       </c>
       <c r="D169">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E169">
-        <v>40.2</v>
+        <v>30</v>
       </c>
       <c r="F169">
-        <v>0.419</v>
+        <v>0.216</v>
       </c>
       <c r="G169" t="s">
         <v>166</v>
@@ -4723,22 +4723,22 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="B170">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="D170">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E170">
-        <v>39</v>
+        <v>28.2</v>
       </c>
       <c r="F170">
-        <v>0.061</v>
+        <v>0.739</v>
       </c>
       <c r="G170" t="s">
         <v>167</v>

--- a/Astro/predictions_dataset.xlsx
+++ b/Astro/predictions_dataset.xlsx
@@ -37,487 +37,487 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>10.04.202610</t>
-  </si>
-  <si>
-    <t>10.04.202611</t>
-  </si>
-  <si>
-    <t>10.04.202612</t>
-  </si>
-  <si>
-    <t>10.04.202613</t>
-  </si>
-  <si>
-    <t>10.04.202614</t>
-  </si>
-  <si>
-    <t>10.04.202615</t>
-  </si>
-  <si>
-    <t>10.04.202616</t>
-  </si>
-  <si>
-    <t>10.04.202617</t>
-  </si>
-  <si>
-    <t>10.04.202618</t>
-  </si>
-  <si>
-    <t>10.04.202619</t>
-  </si>
-  <si>
-    <t>10.04.202620</t>
-  </si>
-  <si>
-    <t>10.04.202621</t>
-  </si>
-  <si>
-    <t>10.04.202622</t>
-  </si>
-  <si>
-    <t>10.04.202623</t>
-  </si>
-  <si>
-    <t>11.04.20261</t>
-  </si>
-  <si>
-    <t>11.04.20262</t>
-  </si>
-  <si>
-    <t>11.04.20263</t>
-  </si>
-  <si>
-    <t>11.04.20264</t>
-  </si>
-  <si>
-    <t>11.04.20265</t>
-  </si>
-  <si>
-    <t>11.04.20266</t>
-  </si>
-  <si>
-    <t>11.04.20267</t>
-  </si>
-  <si>
-    <t>11.04.20268</t>
-  </si>
-  <si>
-    <t>11.04.20269</t>
-  </si>
-  <si>
-    <t>11.04.202610</t>
-  </si>
-  <si>
-    <t>11.04.202611</t>
-  </si>
-  <si>
-    <t>11.04.202612</t>
-  </si>
-  <si>
-    <t>11.04.202613</t>
-  </si>
-  <si>
-    <t>11.04.202614</t>
-  </si>
-  <si>
-    <t>11.04.202615</t>
-  </si>
-  <si>
-    <t>11.04.202616</t>
-  </si>
-  <si>
-    <t>11.04.202617</t>
-  </si>
-  <si>
-    <t>11.04.202618</t>
-  </si>
-  <si>
-    <t>11.04.202619</t>
-  </si>
-  <si>
-    <t>11.04.202620</t>
-  </si>
-  <si>
-    <t>11.04.202621</t>
-  </si>
-  <si>
-    <t>11.04.202622</t>
-  </si>
-  <si>
-    <t>11.04.202623</t>
-  </si>
-  <si>
-    <t>12.04.20261</t>
-  </si>
-  <si>
-    <t>12.04.20262</t>
-  </si>
-  <si>
-    <t>12.04.20263</t>
-  </si>
-  <si>
-    <t>12.04.20264</t>
-  </si>
-  <si>
-    <t>12.04.20265</t>
-  </si>
-  <si>
-    <t>12.04.20266</t>
-  </si>
-  <si>
-    <t>12.04.20267</t>
-  </si>
-  <si>
-    <t>12.04.20268</t>
-  </si>
-  <si>
-    <t>12.04.20269</t>
-  </si>
-  <si>
-    <t>12.04.202610</t>
-  </si>
-  <si>
-    <t>12.04.202611</t>
-  </si>
-  <si>
-    <t>12.04.202612</t>
-  </si>
-  <si>
-    <t>12.04.202613</t>
-  </si>
-  <si>
-    <t>12.04.202614</t>
-  </si>
-  <si>
-    <t>12.04.202615</t>
-  </si>
-  <si>
-    <t>12.04.202616</t>
-  </si>
-  <si>
-    <t>12.04.202617</t>
-  </si>
-  <si>
-    <t>12.04.202618</t>
-  </si>
-  <si>
-    <t>12.04.202619</t>
-  </si>
-  <si>
-    <t>12.04.202620</t>
-  </si>
-  <si>
-    <t>12.04.202621</t>
-  </si>
-  <si>
-    <t>12.04.202622</t>
-  </si>
-  <si>
-    <t>12.04.202623</t>
-  </si>
-  <si>
-    <t>13.04.20261</t>
-  </si>
-  <si>
-    <t>13.04.20262</t>
-  </si>
-  <si>
-    <t>13.04.20263</t>
-  </si>
-  <si>
-    <t>13.04.20264</t>
-  </si>
-  <si>
-    <t>13.04.20265</t>
-  </si>
-  <si>
-    <t>13.04.20266</t>
-  </si>
-  <si>
-    <t>13.04.20267</t>
-  </si>
-  <si>
-    <t>13.04.20268</t>
-  </si>
-  <si>
-    <t>13.04.20269</t>
-  </si>
-  <si>
-    <t>13.04.202610</t>
-  </si>
-  <si>
-    <t>13.04.202611</t>
-  </si>
-  <si>
-    <t>13.04.202612</t>
-  </si>
-  <si>
-    <t>13.04.202613</t>
-  </si>
-  <si>
-    <t>13.04.202614</t>
-  </si>
-  <si>
-    <t>13.04.202615</t>
-  </si>
-  <si>
-    <t>13.04.202616</t>
-  </si>
-  <si>
-    <t>13.04.202617</t>
-  </si>
-  <si>
-    <t>13.04.202618</t>
-  </si>
-  <si>
-    <t>13.04.202619</t>
-  </si>
-  <si>
-    <t>13.04.202620</t>
-  </si>
-  <si>
-    <t>13.04.202621</t>
-  </si>
-  <si>
-    <t>13.04.202622</t>
-  </si>
-  <si>
-    <t>13.04.202623</t>
-  </si>
-  <si>
-    <t>14.04.20261</t>
-  </si>
-  <si>
-    <t>14.04.20262</t>
-  </si>
-  <si>
-    <t>14.04.20263</t>
-  </si>
-  <si>
-    <t>14.04.20264</t>
-  </si>
-  <si>
-    <t>14.04.20265</t>
-  </si>
-  <si>
-    <t>14.04.20266</t>
-  </si>
-  <si>
-    <t>14.04.20267</t>
-  </si>
-  <si>
-    <t>14.04.20268</t>
-  </si>
-  <si>
-    <t>14.04.20269</t>
-  </si>
-  <si>
-    <t>14.04.202610</t>
-  </si>
-  <si>
-    <t>14.04.202611</t>
-  </si>
-  <si>
-    <t>14.04.202612</t>
-  </si>
-  <si>
-    <t>14.04.202613</t>
-  </si>
-  <si>
-    <t>14.04.202614</t>
-  </si>
-  <si>
-    <t>14.04.202615</t>
-  </si>
-  <si>
-    <t>14.04.202616</t>
-  </si>
-  <si>
-    <t>14.04.202617</t>
-  </si>
-  <si>
-    <t>14.04.202618</t>
-  </si>
-  <si>
-    <t>14.04.202619</t>
-  </si>
-  <si>
-    <t>14.04.202620</t>
-  </si>
-  <si>
-    <t>14.04.202621</t>
-  </si>
-  <si>
-    <t>14.04.202622</t>
-  </si>
-  <si>
-    <t>14.04.202623</t>
-  </si>
-  <si>
-    <t>15.04.20261</t>
-  </si>
-  <si>
-    <t>15.04.20262</t>
-  </si>
-  <si>
-    <t>15.04.20263</t>
-  </si>
-  <si>
-    <t>15.04.20264</t>
-  </si>
-  <si>
-    <t>15.04.20265</t>
-  </si>
-  <si>
-    <t>15.04.20266</t>
-  </si>
-  <si>
-    <t>15.04.20267</t>
-  </si>
-  <si>
-    <t>15.04.20268</t>
-  </si>
-  <si>
-    <t>15.04.20269</t>
-  </si>
-  <si>
-    <t>15.04.202610</t>
-  </si>
-  <si>
-    <t>15.04.202611</t>
-  </si>
-  <si>
-    <t>15.04.202612</t>
-  </si>
-  <si>
-    <t>15.04.202613</t>
-  </si>
-  <si>
-    <t>15.04.202614</t>
-  </si>
-  <si>
-    <t>15.04.202615</t>
-  </si>
-  <si>
-    <t>15.04.202616</t>
-  </si>
-  <si>
-    <t>15.04.202617</t>
-  </si>
-  <si>
-    <t>15.04.202618</t>
-  </si>
-  <si>
-    <t>15.04.202619</t>
-  </si>
-  <si>
-    <t>15.04.202620</t>
-  </si>
-  <si>
-    <t>15.04.202621</t>
-  </si>
-  <si>
-    <t>15.04.202622</t>
-  </si>
-  <si>
-    <t>15.04.202623</t>
-  </si>
-  <si>
-    <t>16.04.20261</t>
-  </si>
-  <si>
-    <t>16.04.20262</t>
-  </si>
-  <si>
-    <t>16.04.20263</t>
-  </si>
-  <si>
-    <t>16.04.20264</t>
-  </si>
-  <si>
-    <t>16.04.20265</t>
-  </si>
-  <si>
-    <t>16.04.20266</t>
-  </si>
-  <si>
-    <t>16.04.20267</t>
-  </si>
-  <si>
-    <t>16.04.20268</t>
-  </si>
-  <si>
-    <t>16.04.20269</t>
-  </si>
-  <si>
-    <t>16.04.202610</t>
-  </si>
-  <si>
-    <t>16.04.202611</t>
-  </si>
-  <si>
-    <t>16.04.202612</t>
-  </si>
-  <si>
-    <t>16.04.202613</t>
-  </si>
-  <si>
-    <t>16.04.202614</t>
-  </si>
-  <si>
-    <t>16.04.202615</t>
-  </si>
-  <si>
-    <t>16.04.202616</t>
-  </si>
-  <si>
-    <t>16.04.202617</t>
-  </si>
-  <si>
-    <t>16.04.202618</t>
-  </si>
-  <si>
-    <t>16.04.202619</t>
-  </si>
-  <si>
-    <t>16.04.202620</t>
-  </si>
-  <si>
-    <t>16.04.202621</t>
-  </si>
-  <si>
-    <t>16.04.202622</t>
-  </si>
-  <si>
-    <t>16.04.202623</t>
-  </si>
-  <si>
-    <t>17.04.20261</t>
-  </si>
-  <si>
-    <t>17.04.20262</t>
-  </si>
-  <si>
-    <t>17.04.20263</t>
-  </si>
-  <si>
-    <t>17.04.20264</t>
-  </si>
-  <si>
-    <t>17.04.20265</t>
-  </si>
-  <si>
-    <t>17.04.20266</t>
-  </si>
-  <si>
-    <t>17.04.20267</t>
-  </si>
-  <si>
-    <t>17.04.20268</t>
-  </si>
-  <si>
-    <t>17.04.20269</t>
+    <t>04.06.202616</t>
+  </si>
+  <si>
+    <t>04.06.202617</t>
+  </si>
+  <si>
+    <t>04.06.202618</t>
+  </si>
+  <si>
+    <t>04.06.202619</t>
+  </si>
+  <si>
+    <t>04.06.202620</t>
+  </si>
+  <si>
+    <t>04.06.202621</t>
+  </si>
+  <si>
+    <t>04.06.202622</t>
+  </si>
+  <si>
+    <t>04.06.202623</t>
+  </si>
+  <si>
+    <t>05.06.20261</t>
+  </si>
+  <si>
+    <t>05.06.20262</t>
+  </si>
+  <si>
+    <t>05.06.20263</t>
+  </si>
+  <si>
+    <t>05.06.20264</t>
+  </si>
+  <si>
+    <t>05.06.20265</t>
+  </si>
+  <si>
+    <t>05.06.20266</t>
+  </si>
+  <si>
+    <t>05.06.20267</t>
+  </si>
+  <si>
+    <t>05.06.20268</t>
+  </si>
+  <si>
+    <t>05.06.20269</t>
+  </si>
+  <si>
+    <t>05.06.202610</t>
+  </si>
+  <si>
+    <t>05.06.202611</t>
+  </si>
+  <si>
+    <t>05.06.202612</t>
+  </si>
+  <si>
+    <t>05.06.202613</t>
+  </si>
+  <si>
+    <t>05.06.202614</t>
+  </si>
+  <si>
+    <t>05.06.202615</t>
+  </si>
+  <si>
+    <t>05.06.202616</t>
+  </si>
+  <si>
+    <t>05.06.202617</t>
+  </si>
+  <si>
+    <t>05.06.202618</t>
+  </si>
+  <si>
+    <t>05.06.202619</t>
+  </si>
+  <si>
+    <t>05.06.202620</t>
+  </si>
+  <si>
+    <t>05.06.202621</t>
+  </si>
+  <si>
+    <t>05.06.202622</t>
+  </si>
+  <si>
+    <t>05.06.202623</t>
+  </si>
+  <si>
+    <t>06.06.20261</t>
+  </si>
+  <si>
+    <t>06.06.20262</t>
+  </si>
+  <si>
+    <t>06.06.20263</t>
+  </si>
+  <si>
+    <t>06.06.20264</t>
+  </si>
+  <si>
+    <t>06.06.20265</t>
+  </si>
+  <si>
+    <t>06.06.20266</t>
+  </si>
+  <si>
+    <t>06.06.20267</t>
+  </si>
+  <si>
+    <t>06.06.20268</t>
+  </si>
+  <si>
+    <t>06.06.20269</t>
+  </si>
+  <si>
+    <t>06.06.202610</t>
+  </si>
+  <si>
+    <t>06.06.202611</t>
+  </si>
+  <si>
+    <t>06.06.202612</t>
+  </si>
+  <si>
+    <t>06.06.202613</t>
+  </si>
+  <si>
+    <t>06.06.202614</t>
+  </si>
+  <si>
+    <t>06.06.202615</t>
+  </si>
+  <si>
+    <t>06.06.202616</t>
+  </si>
+  <si>
+    <t>06.06.202617</t>
+  </si>
+  <si>
+    <t>06.06.202618</t>
+  </si>
+  <si>
+    <t>06.06.202619</t>
+  </si>
+  <si>
+    <t>06.06.202620</t>
+  </si>
+  <si>
+    <t>06.06.202621</t>
+  </si>
+  <si>
+    <t>06.06.202622</t>
+  </si>
+  <si>
+    <t>06.06.202623</t>
+  </si>
+  <si>
+    <t>07.06.20261</t>
+  </si>
+  <si>
+    <t>07.06.20262</t>
+  </si>
+  <si>
+    <t>07.06.20263</t>
+  </si>
+  <si>
+    <t>07.06.20264</t>
+  </si>
+  <si>
+    <t>07.06.20265</t>
+  </si>
+  <si>
+    <t>07.06.20266</t>
+  </si>
+  <si>
+    <t>07.06.20267</t>
+  </si>
+  <si>
+    <t>07.06.20268</t>
+  </si>
+  <si>
+    <t>07.06.20269</t>
+  </si>
+  <si>
+    <t>07.06.202610</t>
+  </si>
+  <si>
+    <t>07.06.202611</t>
+  </si>
+  <si>
+    <t>07.06.202612</t>
+  </si>
+  <si>
+    <t>07.06.202613</t>
+  </si>
+  <si>
+    <t>07.06.202614</t>
+  </si>
+  <si>
+    <t>07.06.202615</t>
+  </si>
+  <si>
+    <t>07.06.202616</t>
+  </si>
+  <si>
+    <t>07.06.202617</t>
+  </si>
+  <si>
+    <t>07.06.202618</t>
+  </si>
+  <si>
+    <t>07.06.202619</t>
+  </si>
+  <si>
+    <t>07.06.202620</t>
+  </si>
+  <si>
+    <t>07.06.202621</t>
+  </si>
+  <si>
+    <t>07.06.202622</t>
+  </si>
+  <si>
+    <t>07.06.202623</t>
+  </si>
+  <si>
+    <t>08.06.20261</t>
+  </si>
+  <si>
+    <t>08.06.20262</t>
+  </si>
+  <si>
+    <t>08.06.20263</t>
+  </si>
+  <si>
+    <t>08.06.20264</t>
+  </si>
+  <si>
+    <t>08.06.20265</t>
+  </si>
+  <si>
+    <t>08.06.20266</t>
+  </si>
+  <si>
+    <t>08.06.20267</t>
+  </si>
+  <si>
+    <t>08.06.20268</t>
+  </si>
+  <si>
+    <t>08.06.20269</t>
+  </si>
+  <si>
+    <t>08.06.202610</t>
+  </si>
+  <si>
+    <t>08.06.202611</t>
+  </si>
+  <si>
+    <t>08.06.202612</t>
+  </si>
+  <si>
+    <t>08.06.202613</t>
+  </si>
+  <si>
+    <t>08.06.202614</t>
+  </si>
+  <si>
+    <t>08.06.202615</t>
+  </si>
+  <si>
+    <t>08.06.202616</t>
+  </si>
+  <si>
+    <t>08.06.202617</t>
+  </si>
+  <si>
+    <t>08.06.202618</t>
+  </si>
+  <si>
+    <t>08.06.202619</t>
+  </si>
+  <si>
+    <t>08.06.202620</t>
+  </si>
+  <si>
+    <t>08.06.202621</t>
+  </si>
+  <si>
+    <t>08.06.202622</t>
+  </si>
+  <si>
+    <t>08.06.202623</t>
+  </si>
+  <si>
+    <t>09.06.20261</t>
+  </si>
+  <si>
+    <t>09.06.20262</t>
+  </si>
+  <si>
+    <t>09.06.20263</t>
+  </si>
+  <si>
+    <t>09.06.20264</t>
+  </si>
+  <si>
+    <t>09.06.20265</t>
+  </si>
+  <si>
+    <t>09.06.20266</t>
+  </si>
+  <si>
+    <t>09.06.20267</t>
+  </si>
+  <si>
+    <t>09.06.20268</t>
+  </si>
+  <si>
+    <t>09.06.20269</t>
+  </si>
+  <si>
+    <t>09.06.202610</t>
+  </si>
+  <si>
+    <t>09.06.202611</t>
+  </si>
+  <si>
+    <t>09.06.202612</t>
+  </si>
+  <si>
+    <t>09.06.202613</t>
+  </si>
+  <si>
+    <t>09.06.202614</t>
+  </si>
+  <si>
+    <t>09.06.202615</t>
+  </si>
+  <si>
+    <t>09.06.202616</t>
+  </si>
+  <si>
+    <t>09.06.202617</t>
+  </si>
+  <si>
+    <t>09.06.202618</t>
+  </si>
+  <si>
+    <t>09.06.202619</t>
+  </si>
+  <si>
+    <t>09.06.202620</t>
+  </si>
+  <si>
+    <t>09.06.202621</t>
+  </si>
+  <si>
+    <t>09.06.202622</t>
+  </si>
+  <si>
+    <t>09.06.202623</t>
+  </si>
+  <si>
+    <t>10.06.20261</t>
+  </si>
+  <si>
+    <t>10.06.20262</t>
+  </si>
+  <si>
+    <t>10.06.20263</t>
+  </si>
+  <si>
+    <t>10.06.20264</t>
+  </si>
+  <si>
+    <t>10.06.20265</t>
+  </si>
+  <si>
+    <t>10.06.20266</t>
+  </si>
+  <si>
+    <t>10.06.20267</t>
+  </si>
+  <si>
+    <t>10.06.20268</t>
+  </si>
+  <si>
+    <t>10.06.20269</t>
+  </si>
+  <si>
+    <t>10.06.202610</t>
+  </si>
+  <si>
+    <t>10.06.202611</t>
+  </si>
+  <si>
+    <t>10.06.202612</t>
+  </si>
+  <si>
+    <t>10.06.202613</t>
+  </si>
+  <si>
+    <t>10.06.202614</t>
+  </si>
+  <si>
+    <t>10.06.202615</t>
+  </si>
+  <si>
+    <t>10.06.202616</t>
+  </si>
+  <si>
+    <t>10.06.202617</t>
+  </si>
+  <si>
+    <t>10.06.202618</t>
+  </si>
+  <si>
+    <t>10.06.202619</t>
+  </si>
+  <si>
+    <t>10.06.202620</t>
+  </si>
+  <si>
+    <t>10.06.202621</t>
+  </si>
+  <si>
+    <t>10.06.202622</t>
+  </si>
+  <si>
+    <t>10.06.202623</t>
+  </si>
+  <si>
+    <t>11.06.20261</t>
+  </si>
+  <si>
+    <t>11.06.20262</t>
+  </si>
+  <si>
+    <t>11.06.20263</t>
+  </si>
+  <si>
+    <t>11.06.20264</t>
+  </si>
+  <si>
+    <t>11.06.20265</t>
+  </si>
+  <si>
+    <t>11.06.20266</t>
+  </si>
+  <si>
+    <t>11.06.20267</t>
+  </si>
+  <si>
+    <t>11.06.20268</t>
+  </si>
+  <si>
+    <t>11.06.20269</t>
+  </si>
+  <si>
+    <t>11.06.202610</t>
+  </si>
+  <si>
+    <t>11.06.202611</t>
+  </si>
+  <si>
+    <t>11.06.202612</t>
+  </si>
+  <si>
+    <t>11.06.202613</t>
+  </si>
+  <si>
+    <t>11.06.202614</t>
+  </si>
+  <si>
+    <t>11.06.202615</t>
   </si>
 </sst>
 </file>
@@ -907,10 +907,10 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46122</v>
+        <v>46177</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -924,10 +924,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46122</v>
+        <v>46177</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -947,19 +947,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46122</v>
+        <v>46177</v>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C4">
-        <v>728</v>
+        <v>452</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -970,22 +970,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46122</v>
+        <v>46177</v>
       </c>
       <c r="B5">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C5">
-        <v>774</v>
+        <v>186</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>45.6</v>
       </c>
       <c r="F5">
-        <v>3.238</v>
+        <v>1.326</v>
       </c>
       <c r="G5" t="s">
         <v>9</v>
@@ -993,22 +993,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46122</v>
+        <v>46177</v>
       </c>
       <c r="B6">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C6">
-        <v>707</v>
+        <v>111</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>38.2</v>
       </c>
       <c r="F6">
-        <v>2.961</v>
+        <v>0.514</v>
       </c>
       <c r="G6" t="s">
         <v>10</v>
@@ -1016,22 +1016,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46122</v>
+        <v>46177</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C7">
-        <v>608</v>
+        <v>31</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E7">
-        <v>24</v>
+        <v>38.5</v>
       </c>
       <c r="F7">
-        <v>2.632</v>
+        <v>0.239</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
@@ -1039,22 +1039,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46122</v>
+        <v>46177</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C8">
-        <v>508</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F8">
-        <v>2.421</v>
+        <v>0.05</v>
       </c>
       <c r="G8" t="s">
         <v>12</v>
@@ -1062,22 +1062,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46122</v>
+        <v>46177</v>
       </c>
       <c r="B9">
+        <v>22</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
         <v>16</v>
       </c>
-      <c r="C9">
-        <v>398</v>
-      </c>
-      <c r="D9">
-        <v>9</v>
-      </c>
       <c r="E9">
-        <v>31.6</v>
+        <v>29</v>
       </c>
       <c r="F9">
-        <v>1.856</v>
+        <v>0</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -1085,22 +1085,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46122</v>
+        <v>46177</v>
       </c>
       <c r="B10">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C10">
-        <v>282</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E10">
-        <v>31.8</v>
+        <v>27.4</v>
       </c>
       <c r="F10">
-        <v>1.687</v>
+        <v>0</v>
       </c>
       <c r="G10" t="s">
         <v>14</v>
@@ -1108,177 +1108,177 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46122</v>
+        <v>46178</v>
       </c>
       <c r="B11">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E11">
-        <v>29.4</v>
-      </c>
-      <c r="F11">
-        <v>1.091</v>
-      </c>
-      <c r="G11" t="s">
-        <v>15</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46122</v>
+        <v>46178</v>
       </c>
       <c r="B12">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E12">
-        <v>30.2</v>
+        <v>25.9</v>
       </c>
       <c r="F12">
-        <v>0.438</v>
+        <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46122</v>
+        <v>46178</v>
       </c>
       <c r="B13">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E13">
-        <v>30.5</v>
+        <v>25.9</v>
       </c>
       <c r="F13">
-        <v>0.06900000000000001</v>
+        <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46122</v>
+        <v>46178</v>
       </c>
       <c r="B14">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E14">
-        <v>29</v>
+        <v>25.1</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46122</v>
+        <v>46178</v>
       </c>
       <c r="B15">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E15">
-        <v>28.2</v>
+        <v>25.1</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46122</v>
+        <v>46178</v>
       </c>
       <c r="B16">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E16">
-        <v>29.7</v>
+        <v>26.7</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46123</v>
+        <v>46178</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E17">
-        <v>27.4</v>
+        <v>27.9</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46123</v>
+        <v>46178</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E18">
-        <v>25.1</v>
+        <v>23.4</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="G18" t="s">
         <v>21</v>
@@ -1286,22 +1286,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46123</v>
+        <v>46178</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E19">
-        <v>25.1</v>
+        <v>18.9</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>0.398</v>
       </c>
       <c r="G19" t="s">
         <v>22</v>
@@ -1309,22 +1309,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46123</v>
+        <v>46178</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E20">
-        <v>25.1</v>
+        <v>18.6</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>0.832</v>
       </c>
       <c r="G20" t="s">
         <v>23</v>
@@ -1332,22 +1332,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46123</v>
+        <v>46178</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E21">
-        <v>27.4</v>
+        <v>19.3</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1.493</v>
       </c>
       <c r="G21" t="s">
         <v>24</v>
@@ -1355,22 +1355,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46123</v>
+        <v>46178</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>668</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E22">
-        <v>31.2</v>
+        <v>18.6</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1.924</v>
       </c>
       <c r="G22" t="s">
         <v>25</v>
@@ -1378,22 +1378,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46123</v>
+        <v>46178</v>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>727</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E23">
-        <v>34.2</v>
+        <v>18</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>2.421</v>
       </c>
       <c r="G23" t="s">
         <v>26</v>
@@ -1401,22 +1401,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46123</v>
+        <v>46178</v>
       </c>
       <c r="B24">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C24">
-        <v>49</v>
+        <v>743</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E24">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>2.591</v>
       </c>
       <c r="G24" t="s">
         <v>27</v>
@@ -1424,22 +1424,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46123</v>
+        <v>46178</v>
       </c>
       <c r="B25">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C25">
-        <v>169</v>
+        <v>699</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E25">
-        <v>31.7</v>
+        <v>20</v>
       </c>
       <c r="F25">
-        <v>0.154</v>
+        <v>2.638</v>
       </c>
       <c r="G25" t="s">
         <v>28</v>
@@ -1447,22 +1447,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46123</v>
+        <v>46178</v>
       </c>
       <c r="B26">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>300</v>
+        <v>608</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E26">
-        <v>30.3</v>
+        <v>23.6</v>
       </c>
       <c r="F26">
-        <v>0.6909999999999999</v>
+        <v>2.459</v>
       </c>
       <c r="G26" t="s">
         <v>29</v>
@@ -1470,22 +1470,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46123</v>
+        <v>46178</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C27">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E27">
-        <v>27.9</v>
+        <v>34.5</v>
       </c>
       <c r="F27">
-        <v>1.175</v>
+        <v>1.983</v>
       </c>
       <c r="G27" t="s">
         <v>30</v>
@@ -1493,22 +1493,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46123</v>
+        <v>46178</v>
       </c>
       <c r="B28">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C28">
-        <v>520</v>
+        <v>299</v>
       </c>
       <c r="D28">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E28">
-        <v>27.5</v>
+        <v>43.2</v>
       </c>
       <c r="F28">
-        <v>1.871</v>
+        <v>1.579</v>
       </c>
       <c r="G28" t="s">
         <v>31</v>
@@ -1516,22 +1516,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46123</v>
+        <v>46178</v>
       </c>
       <c r="B29">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C29">
-        <v>558</v>
+        <v>210</v>
       </c>
       <c r="D29">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E29">
-        <v>29.9</v>
+        <v>41.3</v>
       </c>
       <c r="F29">
-        <v>2.031</v>
+        <v>1.061</v>
       </c>
       <c r="G29" t="s">
         <v>32</v>
@@ -1539,22 +1539,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46123</v>
+        <v>46178</v>
       </c>
       <c r="B30">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C30">
-        <v>547</v>
+        <v>120</v>
       </c>
       <c r="D30">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E30">
-        <v>33.3</v>
+        <v>38.5</v>
       </c>
       <c r="F30">
-        <v>2.02</v>
+        <v>0.588</v>
       </c>
       <c r="G30" t="s">
         <v>33</v>
@@ -1562,22 +1562,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46123</v>
+        <v>46178</v>
       </c>
       <c r="B31">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C31">
-        <v>506</v>
+        <v>34</v>
       </c>
       <c r="D31">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E31">
-        <v>35.9</v>
+        <v>41.6</v>
       </c>
       <c r="F31">
-        <v>2.062</v>
+        <v>0.266</v>
       </c>
       <c r="G31" t="s">
         <v>34</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46123</v>
+        <v>46178</v>
       </c>
       <c r="B32">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C32">
-        <v>435</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E32">
-        <v>38.1</v>
+        <v>41.3</v>
       </c>
       <c r="F32">
-        <v>1.985</v>
+        <v>0.055</v>
       </c>
       <c r="G32" t="s">
         <v>35</v>
@@ -1608,22 +1608,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46123</v>
+        <v>46178</v>
       </c>
       <c r="B33">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C33">
-        <v>349</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E33">
-        <v>38.7</v>
+        <v>39.9</v>
       </c>
       <c r="F33">
-        <v>1.934</v>
+        <v>0</v>
       </c>
       <c r="G33" t="s">
         <v>36</v>
@@ -1631,22 +1631,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46123</v>
+        <v>46178</v>
       </c>
       <c r="B34">
+        <v>23</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
         <v>17</v>
       </c>
-      <c r="C34">
-        <v>257</v>
-      </c>
-      <c r="D34">
-        <v>10</v>
-      </c>
       <c r="E34">
-        <v>35.4</v>
+        <v>39.9</v>
       </c>
       <c r="F34">
-        <v>1.532</v>
+        <v>0</v>
       </c>
       <c r="G34" t="s">
         <v>37</v>
@@ -1654,177 +1654,177 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46123</v>
+        <v>46179</v>
       </c>
       <c r="B35">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E35">
-        <v>30.5</v>
-      </c>
-      <c r="F35">
-        <v>0.901</v>
-      </c>
-      <c r="G35" t="s">
-        <v>38</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46123</v>
+        <v>46179</v>
       </c>
       <c r="B36">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E36">
-        <v>31.6</v>
+        <v>39.2</v>
       </c>
       <c r="F36">
-        <v>0.395</v>
+        <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46123</v>
+        <v>46179</v>
       </c>
       <c r="B37">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E37">
-        <v>28.9</v>
+        <v>38.5</v>
       </c>
       <c r="F37">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46123</v>
+        <v>46179</v>
       </c>
       <c r="B38">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E38">
-        <v>23.5</v>
+        <v>39.2</v>
       </c>
       <c r="F38">
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46123</v>
+        <v>46179</v>
       </c>
       <c r="B39">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E39">
-        <v>21.1</v>
+        <v>39.9</v>
       </c>
       <c r="F39">
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46123</v>
+        <v>46179</v>
       </c>
       <c r="B40">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E40">
-        <v>17.9</v>
+        <v>40.6</v>
       </c>
       <c r="F40">
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46124</v>
+        <v>46179</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E41">
-        <v>13.7</v>
+        <v>40.6</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46124</v>
+        <v>46179</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E42">
-        <v>7.7</v>
+        <v>40.7</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="G42" t="s">
         <v>44</v>
@@ -1832,22 +1832,22 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46124</v>
+        <v>46179</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E43">
-        <v>2.4</v>
+        <v>44</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>0.405</v>
       </c>
       <c r="G43" t="s">
         <v>45</v>
@@ -1855,22 +1855,22 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46124</v>
+        <v>46179</v>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>42.4</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>0.838</v>
       </c>
       <c r="G44" t="s">
         <v>46</v>
@@ -1878,22 +1878,22 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46124</v>
+        <v>46179</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>434</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>39.4</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="G45" t="s">
         <v>47</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46124</v>
+        <v>46179</v>
       </c>
       <c r="B46">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>39.6</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>1.563</v>
       </c>
       <c r="G46" t="s">
         <v>48</v>
@@ -1924,22 +1924,22 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46124</v>
+        <v>46179</v>
       </c>
       <c r="B47">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>534</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>1.729</v>
       </c>
       <c r="G47" t="s">
         <v>49</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46124</v>
+        <v>46179</v>
       </c>
       <c r="B48">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C48">
-        <v>74</v>
+        <v>574</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>1.827</v>
       </c>
       <c r="G48" t="s">
         <v>50</v>
@@ -1970,22 +1970,22 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46124</v>
+        <v>46179</v>
       </c>
       <c r="B49">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C49">
-        <v>242</v>
+        <v>613</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F49">
-        <v>0.19</v>
+        <v>2.067</v>
       </c>
       <c r="G49" t="s">
         <v>51</v>
@@ -1993,22 +1993,22 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46124</v>
+        <v>46179</v>
       </c>
       <c r="B50">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C50">
-        <v>424</v>
+        <v>585</v>
       </c>
       <c r="D50">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>27.6</v>
       </c>
       <c r="F50">
-        <v>0.9330000000000001</v>
+        <v>2.205</v>
       </c>
       <c r="G50" t="s">
         <v>52</v>
@@ -2016,22 +2016,22 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46124</v>
+        <v>46179</v>
       </c>
       <c r="B51">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C51">
-        <v>588</v>
+        <v>480</v>
       </c>
       <c r="D51">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F51">
-        <v>1.932</v>
+        <v>1.911</v>
       </c>
       <c r="G51" t="s">
         <v>53</v>
@@ -2039,22 +2039,22 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46124</v>
+        <v>46179</v>
       </c>
       <c r="B52">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C52">
-        <v>713</v>
+        <v>357</v>
       </c>
       <c r="D52">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>33.1</v>
       </c>
       <c r="F52">
-        <v>2.694</v>
+        <v>1.601</v>
       </c>
       <c r="G52" t="s">
         <v>54</v>
@@ -2062,22 +2062,22 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46124</v>
+        <v>46179</v>
       </c>
       <c r="B53">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C53">
-        <v>788</v>
+        <v>226</v>
       </c>
       <c r="D53">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>38.7</v>
       </c>
       <c r="F53">
-        <v>3.077</v>
+        <v>1.093</v>
       </c>
       <c r="G53" t="s">
         <v>55</v>
@@ -2085,22 +2085,22 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46124</v>
+        <v>46179</v>
       </c>
       <c r="B54">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C54">
-        <v>811</v>
+        <v>113</v>
       </c>
       <c r="D54">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>44.8</v>
       </c>
       <c r="F54">
-        <v>3.132</v>
+        <v>0.618</v>
       </c>
       <c r="G54" t="s">
         <v>56</v>
@@ -2108,22 +2108,22 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46124</v>
+        <v>46179</v>
       </c>
       <c r="B55">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C55">
-        <v>777</v>
+        <v>31</v>
       </c>
       <c r="D55">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>48.1</v>
       </c>
       <c r="F55">
-        <v>3.161</v>
+        <v>0.297</v>
       </c>
       <c r="G55" t="s">
         <v>57</v>
@@ -2131,22 +2131,22 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46124</v>
+        <v>46179</v>
       </c>
       <c r="B56">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C56">
-        <v>689</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F56">
-        <v>3.048</v>
+        <v>0.056</v>
       </c>
       <c r="G56" t="s">
         <v>58</v>
@@ -2154,22 +2154,22 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46124</v>
+        <v>46179</v>
       </c>
       <c r="B57">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C57">
-        <v>554</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F57">
-        <v>2.632</v>
+        <v>0</v>
       </c>
       <c r="G57" t="s">
         <v>59</v>
@@ -2177,22 +2177,22 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46124</v>
+        <v>46179</v>
       </c>
       <c r="B58">
+        <v>23</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
         <v>17</v>
       </c>
-      <c r="C58">
-        <v>384</v>
-      </c>
-      <c r="D58">
-        <v>12</v>
-      </c>
       <c r="E58">
-        <v>0</v>
+        <v>43.4</v>
       </c>
       <c r="F58">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="G58" t="s">
         <v>60</v>
@@ -2200,177 +2200,177 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46124</v>
+        <v>46180</v>
       </c>
       <c r="B59">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C59">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59">
-        <v>1.471</v>
-      </c>
-      <c r="G59" t="s">
-        <v>61</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46124</v>
+        <v>46180</v>
       </c>
       <c r="B60">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E60">
-        <v>1.5</v>
+        <v>50.6</v>
       </c>
       <c r="F60">
-        <v>0.523</v>
+        <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46124</v>
+        <v>46180</v>
       </c>
       <c r="B61">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E61">
-        <v>2.4</v>
+        <v>50.6</v>
       </c>
       <c r="F61">
-        <v>0.066</v>
+        <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46124</v>
+        <v>46180</v>
       </c>
       <c r="B62">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E62">
-        <v>2.4</v>
+        <v>51.2</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46124</v>
+        <v>46180</v>
       </c>
       <c r="B63">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E63">
-        <v>2.4</v>
+        <v>52.4</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46124</v>
+        <v>46180</v>
       </c>
       <c r="B64">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E64">
-        <v>1.5</v>
+        <v>52.4</v>
       </c>
       <c r="F64">
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46125</v>
+        <v>46180</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>53.2</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46125</v>
+        <v>46180</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="G66" t="s">
         <v>67</v>
@@ -2378,22 +2378,22 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46125</v>
+        <v>46180</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="D67">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>0.236</v>
       </c>
       <c r="G67" t="s">
         <v>68</v>
@@ -2401,22 +2401,22 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46125</v>
+        <v>46180</v>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="D68">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>49.4</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>0.704</v>
       </c>
       <c r="G68" t="s">
         <v>69</v>
@@ -2424,22 +2424,22 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46125</v>
+        <v>46180</v>
       </c>
       <c r="B69">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>37.9</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>0.962</v>
       </c>
       <c r="G69" t="s">
         <v>70</v>
@@ -2447,22 +2447,22 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46125</v>
+        <v>46180</v>
       </c>
       <c r="B70">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>1.575</v>
       </c>
       <c r="G70" t="s">
         <v>71</v>
@@ -2470,22 +2470,22 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46125</v>
+        <v>46180</v>
       </c>
       <c r="B71">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>707</v>
       </c>
       <c r="D71">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>2.076</v>
       </c>
       <c r="G71" t="s">
         <v>72</v>
@@ -2493,22 +2493,22 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46125</v>
+        <v>46180</v>
       </c>
       <c r="B72">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C72">
-        <v>75</v>
+        <v>785</v>
       </c>
       <c r="D72">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>2.492</v>
       </c>
       <c r="G72" t="s">
         <v>73</v>
@@ -2516,22 +2516,22 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46125</v>
+        <v>46180</v>
       </c>
       <c r="B73">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C73">
-        <v>242</v>
+        <v>766</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="F73">
-        <v>0.179</v>
+        <v>2.809</v>
       </c>
       <c r="G73" t="s">
         <v>74</v>
@@ -2539,22 +2539,22 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46125</v>
+        <v>46180</v>
       </c>
       <c r="B74">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C74">
-        <v>420</v>
+        <v>704</v>
       </c>
       <c r="D74">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="F74">
-        <v>0.893</v>
+        <v>2.698</v>
       </c>
       <c r="G74" t="s">
         <v>75</v>
@@ -2562,22 +2562,22 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46125</v>
+        <v>46180</v>
       </c>
       <c r="B75">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C75">
-        <v>577</v>
+        <v>606</v>
       </c>
       <c r="D75">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="F75">
-        <v>1.904</v>
+        <v>2.282</v>
       </c>
       <c r="G75" t="s">
         <v>76</v>
@@ -2585,22 +2585,22 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46125</v>
+        <v>46180</v>
       </c>
       <c r="B76">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C76">
-        <v>699</v>
+        <v>461</v>
       </c>
       <c r="D76">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>15.7</v>
       </c>
       <c r="F76">
-        <v>2.608</v>
+        <v>1.94</v>
       </c>
       <c r="G76" t="s">
         <v>77</v>
@@ -2608,22 +2608,22 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46125</v>
+        <v>46180</v>
       </c>
       <c r="B77">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C77">
-        <v>766</v>
+        <v>315</v>
       </c>
       <c r="D77">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E77">
-        <v>1.1</v>
+        <v>17.1</v>
       </c>
       <c r="F77">
-        <v>3.088</v>
+        <v>1.339</v>
       </c>
       <c r="G77" t="s">
         <v>78</v>
@@ -2631,22 +2631,22 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46125</v>
+        <v>46180</v>
       </c>
       <c r="B78">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C78">
-        <v>776</v>
+        <v>177</v>
       </c>
       <c r="D78">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E78">
-        <v>2.6</v>
+        <v>16.7</v>
       </c>
       <c r="F78">
-        <v>3.065</v>
+        <v>0.862</v>
       </c>
       <c r="G78" t="s">
         <v>79</v>
@@ -2654,22 +2654,22 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46125</v>
+        <v>46180</v>
       </c>
       <c r="B79">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C79">
-        <v>737</v>
+        <v>56</v>
       </c>
       <c r="D79">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E79">
-        <v>3.6</v>
+        <v>14.3</v>
       </c>
       <c r="F79">
-        <v>2.974</v>
+        <v>0.276</v>
       </c>
       <c r="G79" t="s">
         <v>80</v>
@@ -2677,22 +2677,22 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46125</v>
+        <v>46180</v>
       </c>
       <c r="B80">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C80">
-        <v>645</v>
+        <v>1</v>
       </c>
       <c r="D80">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E80">
-        <v>5.2</v>
+        <v>9.5</v>
       </c>
       <c r="F80">
-        <v>2.902</v>
+        <v>0.076</v>
       </c>
       <c r="G80" t="s">
         <v>81</v>
@@ -2700,22 +2700,22 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46125</v>
+        <v>46180</v>
       </c>
       <c r="B81">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C81">
-        <v>506</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E81">
-        <v>8.4</v>
+        <v>6.9</v>
       </c>
       <c r="F81">
-        <v>2.393</v>
+        <v>0</v>
       </c>
       <c r="G81" t="s">
         <v>82</v>
@@ -2723,22 +2723,22 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46125</v>
+        <v>46180</v>
       </c>
       <c r="B82">
+        <v>23</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
         <v>17</v>
       </c>
-      <c r="C82">
-        <v>341</v>
-      </c>
-      <c r="D82">
-        <v>14</v>
-      </c>
       <c r="E82">
-        <v>13.1</v>
+        <v>6</v>
       </c>
       <c r="F82">
-        <v>1.987</v>
+        <v>0</v>
       </c>
       <c r="G82" t="s">
         <v>83</v>
@@ -2746,177 +2746,177 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46125</v>
+        <v>46181</v>
       </c>
       <c r="B83">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C83">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E83">
-        <v>20.5</v>
-      </c>
-      <c r="F83">
-        <v>1.224</v>
-      </c>
-      <c r="G83" t="s">
-        <v>84</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46125</v>
+        <v>46181</v>
       </c>
       <c r="B84">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D84">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E84">
-        <v>32.3</v>
+        <v>4.2</v>
       </c>
       <c r="F84">
-        <v>0.457</v>
+        <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46125</v>
+        <v>46181</v>
       </c>
       <c r="B85">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E85">
-        <v>37.8</v>
+        <v>6</v>
       </c>
       <c r="F85">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46125</v>
+        <v>46181</v>
       </c>
       <c r="B86">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E86">
-        <v>39.2</v>
+        <v>6.9</v>
       </c>
       <c r="F86">
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46125</v>
+        <v>46181</v>
       </c>
       <c r="B87">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87">
+        <v>14</v>
+      </c>
+      <c r="E87">
         <v>6</v>
       </c>
-      <c r="E87">
-        <v>39.2</v>
-      </c>
       <c r="F87">
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46125</v>
+        <v>46181</v>
       </c>
       <c r="B88">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D88">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E88">
-        <v>39.2</v>
+        <v>6.9</v>
       </c>
       <c r="F88">
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46126</v>
+        <v>46181</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="D89">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E89">
-        <v>34.9</v>
+        <v>6.6</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46126</v>
+        <v>46181</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="D90">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E90">
-        <v>28.2</v>
+        <v>4.3</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>0.097</v>
       </c>
       <c r="G90" t="s">
         <v>90</v>
@@ -2924,22 +2924,22 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46126</v>
+        <v>46181</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="D91">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E91">
-        <v>25.9</v>
+        <v>5.1</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>0.521</v>
       </c>
       <c r="G91" t="s">
         <v>91</v>
@@ -2947,22 +2947,22 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46126</v>
+        <v>46181</v>
       </c>
       <c r="B92">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>556</v>
       </c>
       <c r="D92">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E92">
-        <v>26.7</v>
+        <v>5.3</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>1.136</v>
       </c>
       <c r="G92" t="s">
         <v>92</v>
@@ -2970,22 +2970,22 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46126</v>
+        <v>46181</v>
       </c>
       <c r="B93">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>697</v>
       </c>
       <c r="D93">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E93">
-        <v>27.4</v>
+        <v>4.7</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>1.856</v>
       </c>
       <c r="G93" t="s">
         <v>93</v>
@@ -2993,22 +2993,22 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46126</v>
+        <v>46181</v>
       </c>
       <c r="B94">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="D94">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E94">
-        <v>22.7</v>
+        <v>8.1</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>2.417</v>
       </c>
       <c r="G94" t="s">
         <v>94</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46126</v>
+        <v>46181</v>
       </c>
       <c r="B95">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>828</v>
       </c>
       <c r="D95">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E95">
-        <v>21.9</v>
+        <v>9</v>
       </c>
       <c r="F95">
-        <v>0</v>
+        <v>2.652</v>
       </c>
       <c r="G95" t="s">
         <v>95</v>
@@ -3039,22 +3039,22 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46126</v>
+        <v>46181</v>
       </c>
       <c r="B96">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C96">
-        <v>56</v>
+        <v>855</v>
       </c>
       <c r="D96">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E96">
-        <v>25.8</v>
+        <v>8</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>2.971</v>
       </c>
       <c r="G96" t="s">
         <v>96</v>
@@ -3062,22 +3062,22 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46126</v>
+        <v>46181</v>
       </c>
       <c r="B97">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C97">
-        <v>197</v>
+        <v>810</v>
       </c>
       <c r="D97">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E97">
-        <v>17.9</v>
+        <v>10</v>
       </c>
       <c r="F97">
-        <v>0.179</v>
+        <v>2.966</v>
       </c>
       <c r="G97" t="s">
         <v>97</v>
@@ -3085,22 +3085,22 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46126</v>
+        <v>46181</v>
       </c>
       <c r="B98">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C98">
-        <v>350</v>
+        <v>730</v>
       </c>
       <c r="D98">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E98">
-        <v>16.1</v>
+        <v>10.6</v>
       </c>
       <c r="F98">
-        <v>0.773</v>
+        <v>2.765</v>
       </c>
       <c r="G98" t="s">
         <v>98</v>
@@ -3108,22 +3108,22 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46126</v>
+        <v>46181</v>
       </c>
       <c r="B99">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C99">
-        <v>448</v>
+        <v>630</v>
       </c>
       <c r="D99">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E99">
-        <v>22.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F99">
-        <v>1.553</v>
+        <v>2.368</v>
       </c>
       <c r="G99" t="s">
         <v>99</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46126</v>
+        <v>46181</v>
       </c>
       <c r="B100">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C100">
         <v>496</v>
       </c>
       <c r="D100">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E100">
-        <v>29</v>
+        <v>8.9</v>
       </c>
       <c r="F100">
-        <v>1.885</v>
+        <v>2.099</v>
       </c>
       <c r="G100" t="s">
         <v>100</v>
@@ -3154,22 +3154,22 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46126</v>
+        <v>46181</v>
       </c>
       <c r="B101">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C101">
-        <v>525</v>
+        <v>341</v>
       </c>
       <c r="D101">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E101">
-        <v>32.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F101">
-        <v>2.004</v>
+        <v>1.45</v>
       </c>
       <c r="G101" t="s">
         <v>101</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46126</v>
+        <v>46181</v>
       </c>
       <c r="B102">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C102">
-        <v>542</v>
+        <v>187</v>
       </c>
       <c r="D102">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E102">
-        <v>32.2</v>
+        <v>8</v>
       </c>
       <c r="F102">
-        <v>1.98</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="G102" t="s">
         <v>102</v>
@@ -3200,22 +3200,22 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46126</v>
+        <v>46181</v>
       </c>
       <c r="B103">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C103">
-        <v>536</v>
+        <v>54</v>
       </c>
       <c r="D103">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E103">
-        <v>30.3</v>
+        <v>10.2</v>
       </c>
       <c r="F103">
-        <v>2.016</v>
+        <v>0.313</v>
       </c>
       <c r="G103" t="s">
         <v>103</v>
@@ -3223,22 +3223,22 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46126</v>
+        <v>46181</v>
       </c>
       <c r="B104">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C104">
-        <v>507</v>
+        <v>1</v>
       </c>
       <c r="D104">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E104">
-        <v>26</v>
+        <v>9.5</v>
       </c>
       <c r="F104">
-        <v>2.049</v>
+        <v>0.056</v>
       </c>
       <c r="G104" t="s">
         <v>104</v>
@@ -3246,22 +3246,22 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46126</v>
+        <v>46181</v>
       </c>
       <c r="B105">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C105">
-        <v>436</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E105">
-        <v>21.8</v>
+        <v>7.7</v>
       </c>
       <c r="F105">
-        <v>1.994</v>
+        <v>0</v>
       </c>
       <c r="G105" t="s">
         <v>105</v>
@@ -3269,22 +3269,22 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46126</v>
+        <v>46181</v>
       </c>
       <c r="B106">
+        <v>23</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+      <c r="D106">
         <v>17</v>
       </c>
-      <c r="C106">
-        <v>318</v>
-      </c>
-      <c r="D106">
-        <v>15</v>
-      </c>
       <c r="E106">
-        <v>19.6</v>
+        <v>7.7</v>
       </c>
       <c r="F106">
-        <v>1.825</v>
+        <v>0</v>
       </c>
       <c r="G106" t="s">
         <v>106</v>
@@ -3292,177 +3292,177 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46126</v>
+        <v>46182</v>
       </c>
       <c r="B107">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E107">
-        <v>20.9</v>
-      </c>
-      <c r="F107">
-        <v>1.135</v>
-      </c>
-      <c r="G107" t="s">
-        <v>107</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46126</v>
+        <v>46182</v>
       </c>
       <c r="B108">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C108">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E108">
-        <v>24.7</v>
+        <v>4.2</v>
       </c>
       <c r="F108">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="G108" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46126</v>
+        <v>46182</v>
       </c>
       <c r="B109">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C109">
         <v>0</v>
       </c>
       <c r="D109">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E109">
-        <v>23.5</v>
+        <v>4.2</v>
       </c>
       <c r="F109">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46126</v>
+        <v>46182</v>
       </c>
       <c r="B110">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C110">
         <v>0</v>
       </c>
       <c r="D110">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E110">
-        <v>22.7</v>
+        <v>3.3</v>
       </c>
       <c r="F110">
         <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46126</v>
+        <v>46182</v>
       </c>
       <c r="B111">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C111">
         <v>0</v>
       </c>
       <c r="D111">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E111">
-        <v>21.9</v>
+        <v>2.4</v>
       </c>
       <c r="F111">
         <v>0</v>
       </c>
       <c r="G111" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46126</v>
+        <v>46182</v>
       </c>
       <c r="B112">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D112">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E112">
-        <v>21.1</v>
+        <v>3.3</v>
       </c>
       <c r="F112">
         <v>0</v>
       </c>
       <c r="G112" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46127</v>
+        <v>46182</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D113">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E113">
-        <v>17.9</v>
+        <v>3.2</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46127</v>
+        <v>46182</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="D114">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E114">
-        <v>12</v>
+        <v>1.6</v>
       </c>
       <c r="F114">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="G114" t="s">
         <v>113</v>
@@ -3470,22 +3470,22 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46127</v>
+        <v>46182</v>
       </c>
       <c r="B115">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>399</v>
       </c>
       <c r="D115">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E115">
-        <v>6</v>
+        <v>1.2</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>0.458</v>
       </c>
       <c r="G115" t="s">
         <v>114</v>
@@ -3493,22 +3493,22 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46127</v>
+        <v>46182</v>
       </c>
       <c r="B116">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="D116">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E116">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>1.129</v>
       </c>
       <c r="G116" t="s">
         <v>115</v>
@@ -3516,22 +3516,22 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46127</v>
+        <v>46182</v>
       </c>
       <c r="B117">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>699</v>
       </c>
       <c r="D117">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E117">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>1.839</v>
       </c>
       <c r="G117" t="s">
         <v>116</v>
@@ -3539,22 +3539,22 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46127</v>
+        <v>46182</v>
       </c>
       <c r="B118">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>803</v>
       </c>
       <c r="D118">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E118">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>2.462</v>
       </c>
       <c r="G118" t="s">
         <v>117</v>
@@ -3562,22 +3562,22 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46127</v>
+        <v>46182</v>
       </c>
       <c r="B119">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>859</v>
       </c>
       <c r="D119">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E119">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>2.808</v>
       </c>
       <c r="G119" t="s">
         <v>118</v>
@@ -3585,22 +3585,22 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46127</v>
+        <v>46182</v>
       </c>
       <c r="B120">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C120">
-        <v>80</v>
+        <v>869</v>
       </c>
       <c r="D120">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E120">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="F120">
-        <v>0</v>
+        <v>2.985</v>
       </c>
       <c r="G120" t="s">
         <v>119</v>
@@ -3608,22 +3608,22 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46127</v>
+        <v>46182</v>
       </c>
       <c r="B121">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C121">
-        <v>244</v>
+        <v>831</v>
       </c>
       <c r="D121">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="E121">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="F121">
-        <v>0.228</v>
+        <v>2.929</v>
       </c>
       <c r="G121" t="s">
         <v>120</v>
@@ -3631,22 +3631,22 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46127</v>
+        <v>46182</v>
       </c>
       <c r="B122">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C122">
-        <v>420</v>
+        <v>749</v>
       </c>
       <c r="D122">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E122">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="F122">
-        <v>0.914</v>
+        <v>2.798</v>
       </c>
       <c r="G122" t="s">
         <v>121</v>
@@ -3654,22 +3654,22 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46127</v>
+        <v>46182</v>
       </c>
       <c r="B123">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C123">
-        <v>581</v>
+        <v>634</v>
       </c>
       <c r="D123">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E123">
-        <v>0.6</v>
+        <v>7.2</v>
       </c>
       <c r="F123">
-        <v>1.899</v>
+        <v>2.569</v>
       </c>
       <c r="G123" t="s">
         <v>122</v>
@@ -3677,22 +3677,22 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46127</v>
+        <v>46182</v>
       </c>
       <c r="B124">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C124">
-        <v>707</v>
+        <v>492</v>
       </c>
       <c r="D124">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="F124">
-        <v>2.567</v>
+        <v>2.109</v>
       </c>
       <c r="G124" t="s">
         <v>123</v>
@@ -3700,22 +3700,22 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46127</v>
+        <v>46182</v>
       </c>
       <c r="B125">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C125">
-        <v>785</v>
+        <v>335</v>
       </c>
       <c r="D125">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F125">
-        <v>3.049</v>
+        <v>1.44</v>
       </c>
       <c r="G125" t="s">
         <v>124</v>
@@ -3723,22 +3723,22 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46127</v>
+        <v>46182</v>
       </c>
       <c r="B126">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C126">
-        <v>804</v>
+        <v>179</v>
       </c>
       <c r="D126">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E126">
-        <v>0.6</v>
+        <v>10</v>
       </c>
       <c r="F126">
-        <v>3.26</v>
+        <v>0.788</v>
       </c>
       <c r="G126" t="s">
         <v>125</v>
@@ -3746,22 +3746,22 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46127</v>
+        <v>46182</v>
       </c>
       <c r="B127">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C127">
-        <v>768</v>
+        <v>52</v>
       </c>
       <c r="D127">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E127">
-        <v>1.1</v>
+        <v>12.7</v>
       </c>
       <c r="F127">
-        <v>3.203</v>
+        <v>0.281</v>
       </c>
       <c r="G127" t="s">
         <v>126</v>
@@ -3769,22 +3769,22 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46127</v>
+        <v>46182</v>
       </c>
       <c r="B128">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C128">
-        <v>674</v>
+        <v>1</v>
       </c>
       <c r="D128">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E128">
-        <v>2.7</v>
+        <v>12</v>
       </c>
       <c r="F128">
-        <v>2.992</v>
+        <v>0.059</v>
       </c>
       <c r="G128" t="s">
         <v>127</v>
@@ -3792,22 +3792,22 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46127</v>
+        <v>46182</v>
       </c>
       <c r="B129">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C129">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="D129">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E129">
-        <v>5.8</v>
+        <v>11.2</v>
       </c>
       <c r="F129">
-        <v>2.588</v>
+        <v>0</v>
       </c>
       <c r="G129" t="s">
         <v>128</v>
@@ -3815,22 +3815,22 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46127</v>
+        <v>46182</v>
       </c>
       <c r="B130">
+        <v>23</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+      <c r="D130">
         <v>17</v>
       </c>
-      <c r="C130">
-        <v>361</v>
-      </c>
-      <c r="D130">
-        <v>16</v>
-      </c>
       <c r="E130">
-        <v>10.3</v>
+        <v>11.2</v>
       </c>
       <c r="F130">
-        <v>2.107</v>
+        <v>0</v>
       </c>
       <c r="G130" t="s">
         <v>129</v>
@@ -3838,177 +3838,177 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46127</v>
+        <v>46183</v>
       </c>
       <c r="B131">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C131">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="D131">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E131">
-        <v>13.1</v>
-      </c>
-      <c r="F131">
-        <v>1.27</v>
-      </c>
-      <c r="G131" t="s">
-        <v>130</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46127</v>
+        <v>46183</v>
       </c>
       <c r="B132">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C132">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E132">
-        <v>12.6</v>
+        <v>11.2</v>
       </c>
       <c r="F132">
-        <v>0.496</v>
+        <v>0</v>
       </c>
       <c r="G132" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46127</v>
+        <v>46183</v>
       </c>
       <c r="B133">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C133">
         <v>0</v>
       </c>
       <c r="D133">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E133">
-        <v>9.5</v>
+        <v>11.2</v>
       </c>
       <c r="F133">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="G133" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46127</v>
+        <v>46183</v>
       </c>
       <c r="B134">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C134">
         <v>0</v>
       </c>
       <c r="D134">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E134">
-        <v>8.6</v>
+        <v>10.3</v>
       </c>
       <c r="F134">
         <v>0</v>
       </c>
       <c r="G134" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46127</v>
+        <v>46183</v>
       </c>
       <c r="B135">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C135">
         <v>0</v>
       </c>
       <c r="D135">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E135">
-        <v>11.2</v>
+        <v>10.3</v>
       </c>
       <c r="F135">
         <v>0</v>
       </c>
       <c r="G135" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46127</v>
+        <v>46183</v>
       </c>
       <c r="B136">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D136">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E136">
-        <v>14.6</v>
+        <v>11.2</v>
       </c>
       <c r="F136">
         <v>0</v>
       </c>
       <c r="G136" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46128</v>
+        <v>46183</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="D137">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E137">
-        <v>13.7</v>
+        <v>11.5</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+      <c r="G137" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46128</v>
+        <v>46183</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="D138">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E138">
-        <v>9.5</v>
+        <v>10.1</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="G138" t="s">
         <v>136</v>
@@ -4016,22 +4016,22 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46128</v>
+        <v>46183</v>
       </c>
       <c r="B139">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>354</v>
       </c>
       <c r="D139">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E139">
-        <v>5.1</v>
+        <v>9.5</v>
       </c>
       <c r="F139">
-        <v>0</v>
+        <v>0.436</v>
       </c>
       <c r="G139" t="s">
         <v>137</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46128</v>
+        <v>46183</v>
       </c>
       <c r="B140">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="D140">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E140">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="F140">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="G140" t="s">
         <v>138</v>
@@ -4062,22 +4062,22 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46128</v>
+        <v>46183</v>
       </c>
       <c r="B141">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>635</v>
       </c>
       <c r="D141">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E141">
-        <v>2.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>1.395</v>
       </c>
       <c r="G141" t="s">
         <v>139</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46128</v>
+        <v>46183</v>
       </c>
       <c r="B142">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="D142">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E142">
-        <v>2.4</v>
+        <v>9.1</v>
       </c>
       <c r="F142">
-        <v>0</v>
+        <v>1.898</v>
       </c>
       <c r="G142" t="s">
         <v>140</v>
@@ -4108,22 +4108,22 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46128</v>
+        <v>46183</v>
       </c>
       <c r="B143">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C143">
-        <v>2</v>
+        <v>774</v>
       </c>
       <c r="D143">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E143">
-        <v>2.4</v>
+        <v>11</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>2.313</v>
       </c>
       <c r="G143" t="s">
         <v>141</v>
@@ -4131,22 +4131,22 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46128</v>
+        <v>46183</v>
       </c>
       <c r="B144">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C144">
-        <v>84</v>
+        <v>773</v>
       </c>
       <c r="D144">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E144">
-        <v>2.3</v>
+        <v>13.5</v>
       </c>
       <c r="F144">
-        <v>0</v>
+        <v>2.404</v>
       </c>
       <c r="G144" t="s">
         <v>142</v>
@@ -4154,22 +4154,22 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46128</v>
+        <v>46183</v>
       </c>
       <c r="B145">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C145">
-        <v>250</v>
+        <v>728</v>
       </c>
       <c r="D145">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E145">
-        <v>1.6</v>
+        <v>16</v>
       </c>
       <c r="F145">
-        <v>0.229</v>
+        <v>2.553</v>
       </c>
       <c r="G145" t="s">
         <v>143</v>
@@ -4177,22 +4177,22 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46128</v>
+        <v>46183</v>
       </c>
       <c r="B146">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C146">
-        <v>426</v>
+        <v>641</v>
       </c>
       <c r="D146">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E146">
-        <v>1.2</v>
+        <v>19.1</v>
       </c>
       <c r="F146">
-        <v>0.929</v>
+        <v>2.524</v>
       </c>
       <c r="G146" t="s">
         <v>144</v>
@@ -4200,22 +4200,22 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46128</v>
+        <v>46183</v>
       </c>
       <c r="B147">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C147">
-        <v>578</v>
+        <v>531</v>
       </c>
       <c r="D147">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E147">
-        <v>1.6</v>
+        <v>21.4</v>
       </c>
       <c r="F147">
-        <v>1.936</v>
+        <v>2.128</v>
       </c>
       <c r="G147" t="s">
         <v>145</v>
@@ -4223,22 +4223,22 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46128</v>
+        <v>46183</v>
       </c>
       <c r="B148">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C148">
-        <v>694</v>
+        <v>402</v>
       </c>
       <c r="D148">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E148">
-        <v>2.1</v>
+        <v>23.9</v>
       </c>
       <c r="F148">
-        <v>2.48</v>
+        <v>1.759</v>
       </c>
       <c r="G148" t="s">
         <v>146</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46128</v>
+        <v>46183</v>
       </c>
       <c r="B149">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C149">
-        <v>757</v>
+        <v>260</v>
       </c>
       <c r="D149">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E149">
-        <v>3.6</v>
+        <v>28.5</v>
       </c>
       <c r="F149">
-        <v>2.848</v>
+        <v>1.259</v>
       </c>
       <c r="G149" t="s">
         <v>147</v>
@@ -4269,22 +4269,22 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46128</v>
+        <v>46183</v>
       </c>
       <c r="B150">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C150">
-        <v>755</v>
+        <v>128</v>
       </c>
       <c r="D150">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E150">
-        <v>6.6</v>
+        <v>35.3</v>
       </c>
       <c r="F150">
-        <v>2.995</v>
+        <v>0.671</v>
       </c>
       <c r="G150" t="s">
         <v>148</v>
@@ -4292,22 +4292,22 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46128</v>
+        <v>46183</v>
       </c>
       <c r="B151">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C151">
-        <v>706</v>
+        <v>33</v>
       </c>
       <c r="D151">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E151">
-        <v>9.199999999999999</v>
+        <v>43.4</v>
       </c>
       <c r="F151">
-        <v>2.965</v>
+        <v>0.277</v>
       </c>
       <c r="G151" t="s">
         <v>149</v>
@@ -4315,22 +4315,22 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46128</v>
+        <v>46183</v>
       </c>
       <c r="B152">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C152">
-        <v>623</v>
+        <v>1</v>
       </c>
       <c r="D152">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E152">
-        <v>10.3</v>
+        <v>43.4</v>
       </c>
       <c r="F152">
-        <v>2.645</v>
+        <v>0.047</v>
       </c>
       <c r="G152" t="s">
         <v>150</v>
@@ -4338,22 +4338,22 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46128</v>
+        <v>46183</v>
       </c>
       <c r="B153">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C153">
-        <v>506</v>
+        <v>0</v>
       </c>
       <c r="D153">
         <v>15</v>
       </c>
       <c r="E153">
-        <v>10.5</v>
+        <v>42.7</v>
       </c>
       <c r="F153">
-        <v>2.361</v>
+        <v>0</v>
       </c>
       <c r="G153" t="s">
         <v>151</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46128</v>
+        <v>46183</v>
       </c>
       <c r="B154">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C154">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="D154">
         <v>15</v>
       </c>
       <c r="E154">
-        <v>11.3</v>
+        <v>42</v>
       </c>
       <c r="F154">
-        <v>1.913</v>
+        <v>0</v>
       </c>
       <c r="G154" t="s">
         <v>152</v>
@@ -4384,177 +4384,177 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46128</v>
+        <v>46184</v>
       </c>
       <c r="B155">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C155">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="D155">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E155">
-        <v>13</v>
-      </c>
-      <c r="F155">
-        <v>1.226</v>
-      </c>
-      <c r="G155" t="s">
-        <v>153</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46128</v>
+        <v>46184</v>
       </c>
       <c r="B156">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C156">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D156">
         <v>13</v>
       </c>
       <c r="E156">
-        <v>15</v>
+        <v>37.8</v>
       </c>
       <c r="F156">
-        <v>0.499</v>
+        <v>0</v>
       </c>
       <c r="G156" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46128</v>
+        <v>46184</v>
       </c>
       <c r="B157">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C157">
         <v>0</v>
       </c>
       <c r="D157">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E157">
-        <v>14.6</v>
+        <v>35.7</v>
       </c>
       <c r="F157">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="G157" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46128</v>
+        <v>46184</v>
       </c>
       <c r="B158">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C158">
         <v>0</v>
       </c>
       <c r="D158">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E158">
-        <v>13.7</v>
+        <v>34.9</v>
       </c>
       <c r="F158">
         <v>0</v>
       </c>
       <c r="G158" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46128</v>
+        <v>46184</v>
       </c>
       <c r="B159">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C159">
         <v>0</v>
       </c>
       <c r="D159">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E159">
-        <v>12</v>
+        <v>34.9</v>
       </c>
       <c r="F159">
         <v>0</v>
       </c>
       <c r="G159" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46128</v>
+        <v>46184</v>
       </c>
       <c r="B160">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D160">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E160">
-        <v>10.3</v>
+        <v>33.5</v>
       </c>
       <c r="F160">
         <v>0</v>
       </c>
       <c r="G160" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46129</v>
+        <v>46184</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D161">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E161">
-        <v>8.6</v>
+        <v>30.8</v>
+      </c>
+      <c r="F161">
+        <v>0</v>
+      </c>
+      <c r="G161" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46129</v>
+        <v>46184</v>
       </c>
       <c r="B162">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="D162">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E162">
-        <v>6</v>
+        <v>26.3</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="G162" t="s">
         <v>159</v>
@@ -4562,22 +4562,22 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46129</v>
+        <v>46184</v>
       </c>
       <c r="B163">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="D163">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E163">
-        <v>3.3</v>
+        <v>23.1</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>0.427</v>
       </c>
       <c r="G163" t="s">
         <v>160</v>
@@ -4585,22 +4585,22 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46129</v>
+        <v>46184</v>
       </c>
       <c r="B164">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>446</v>
       </c>
       <c r="D164">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E164">
-        <v>6</v>
+        <v>20.1</v>
       </c>
       <c r="F164">
-        <v>0</v>
+        <v>1.012</v>
       </c>
       <c r="G164" t="s">
         <v>161</v>
@@ -4608,22 +4608,22 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46129</v>
+        <v>46184</v>
       </c>
       <c r="B165">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>563</v>
       </c>
       <c r="D165">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E165">
-        <v>12.9</v>
+        <v>19.8</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>1.555</v>
       </c>
       <c r="G165" t="s">
         <v>162</v>
@@ -4631,22 +4631,22 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46129</v>
+        <v>46184</v>
       </c>
       <c r="B166">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>659</v>
       </c>
       <c r="D166">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E166">
-        <v>19.5</v>
+        <v>19.1</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>1.919</v>
       </c>
       <c r="G166" t="s">
         <v>163</v>
@@ -4654,22 +4654,22 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46129</v>
+        <v>46184</v>
       </c>
       <c r="B167">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C167">
-        <v>2</v>
+        <v>733</v>
       </c>
       <c r="D167">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E167">
-        <v>25.9</v>
+        <v>17</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>2.349</v>
       </c>
       <c r="G167" t="s">
         <v>164</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46129</v>
+        <v>46184</v>
       </c>
       <c r="B168">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C168">
-        <v>60</v>
+        <v>768</v>
       </c>
       <c r="D168">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E168">
-        <v>31.2</v>
+        <v>15</v>
       </c>
       <c r="F168">
-        <v>0</v>
+        <v>2.644</v>
       </c>
       <c r="G168" t="s">
         <v>165</v>
@@ -4700,22 +4700,22 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46129</v>
+        <v>46184</v>
       </c>
       <c r="B169">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C169">
-        <v>178</v>
+        <v>747</v>
       </c>
       <c r="D169">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E169">
-        <v>30</v>
+        <v>14.5</v>
       </c>
       <c r="F169">
-        <v>0.216</v>
+        <v>2.764</v>
       </c>
       <c r="G169" t="s">
         <v>166</v>
@@ -4723,22 +4723,22 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46129</v>
+        <v>46184</v>
       </c>
       <c r="B170">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C170">
-        <v>311</v>
+        <v>677</v>
       </c>
       <c r="D170">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E170">
-        <v>28.2</v>
+        <v>15.1</v>
       </c>
       <c r="F170">
-        <v>0.739</v>
+        <v>2.679</v>
       </c>
       <c r="G170" t="s">
         <v>167</v>

--- a/Astro/predictions_dataset.xlsx
+++ b/Astro/predictions_dataset.xlsx
@@ -37,487 +37,487 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>04.06.202616</t>
-  </si>
-  <si>
-    <t>04.06.202617</t>
-  </si>
-  <si>
-    <t>04.06.202618</t>
-  </si>
-  <si>
-    <t>04.06.202619</t>
-  </si>
-  <si>
-    <t>04.06.202620</t>
-  </si>
-  <si>
-    <t>04.06.202621</t>
-  </si>
-  <si>
-    <t>04.06.202622</t>
-  </si>
-  <si>
-    <t>04.06.202623</t>
-  </si>
-  <si>
-    <t>05.06.20261</t>
-  </si>
-  <si>
-    <t>05.06.20262</t>
-  </si>
-  <si>
-    <t>05.06.20263</t>
-  </si>
-  <si>
-    <t>05.06.20264</t>
-  </si>
-  <si>
-    <t>05.06.20265</t>
-  </si>
-  <si>
-    <t>05.06.20266</t>
-  </si>
-  <si>
-    <t>05.06.20267</t>
-  </si>
-  <si>
-    <t>05.06.20268</t>
-  </si>
-  <si>
-    <t>05.06.20269</t>
-  </si>
-  <si>
-    <t>05.06.202610</t>
-  </si>
-  <si>
-    <t>05.06.202611</t>
-  </si>
-  <si>
-    <t>05.06.202612</t>
-  </si>
-  <si>
-    <t>05.06.202613</t>
-  </si>
-  <si>
-    <t>05.06.202614</t>
-  </si>
-  <si>
-    <t>05.06.202615</t>
-  </si>
-  <si>
-    <t>05.06.202616</t>
-  </si>
-  <si>
-    <t>05.06.202617</t>
-  </si>
-  <si>
-    <t>05.06.202618</t>
-  </si>
-  <si>
-    <t>05.06.202619</t>
-  </si>
-  <si>
-    <t>05.06.202620</t>
-  </si>
-  <si>
-    <t>05.06.202621</t>
-  </si>
-  <si>
-    <t>05.06.202622</t>
-  </si>
-  <si>
-    <t>05.06.202623</t>
-  </si>
-  <si>
-    <t>06.06.20261</t>
-  </si>
-  <si>
-    <t>06.06.20262</t>
-  </si>
-  <si>
-    <t>06.06.20263</t>
-  </si>
-  <si>
-    <t>06.06.20264</t>
-  </si>
-  <si>
-    <t>06.06.20265</t>
-  </si>
-  <si>
-    <t>06.06.20266</t>
-  </si>
-  <si>
-    <t>06.06.20267</t>
-  </si>
-  <si>
-    <t>06.06.20268</t>
-  </si>
-  <si>
-    <t>06.06.20269</t>
-  </si>
-  <si>
-    <t>06.06.202610</t>
-  </si>
-  <si>
-    <t>06.06.202611</t>
-  </si>
-  <si>
-    <t>06.06.202612</t>
-  </si>
-  <si>
-    <t>06.06.202613</t>
-  </si>
-  <si>
-    <t>06.06.202614</t>
-  </si>
-  <si>
-    <t>06.06.202615</t>
-  </si>
-  <si>
-    <t>06.06.202616</t>
-  </si>
-  <si>
-    <t>06.06.202617</t>
-  </si>
-  <si>
-    <t>06.06.202618</t>
-  </si>
-  <si>
-    <t>06.06.202619</t>
-  </si>
-  <si>
-    <t>06.06.202620</t>
-  </si>
-  <si>
-    <t>06.06.202621</t>
-  </si>
-  <si>
-    <t>06.06.202622</t>
-  </si>
-  <si>
-    <t>06.06.202623</t>
-  </si>
-  <si>
-    <t>07.06.20261</t>
-  </si>
-  <si>
-    <t>07.06.20262</t>
-  </si>
-  <si>
-    <t>07.06.20263</t>
-  </si>
-  <si>
-    <t>07.06.20264</t>
-  </si>
-  <si>
-    <t>07.06.20265</t>
-  </si>
-  <si>
-    <t>07.06.20266</t>
-  </si>
-  <si>
-    <t>07.06.20267</t>
-  </si>
-  <si>
-    <t>07.06.20268</t>
-  </si>
-  <si>
-    <t>07.06.20269</t>
-  </si>
-  <si>
-    <t>07.06.202610</t>
-  </si>
-  <si>
-    <t>07.06.202611</t>
-  </si>
-  <si>
-    <t>07.06.202612</t>
-  </si>
-  <si>
-    <t>07.06.202613</t>
-  </si>
-  <si>
-    <t>07.06.202614</t>
-  </si>
-  <si>
-    <t>07.06.202615</t>
-  </si>
-  <si>
-    <t>07.06.202616</t>
-  </si>
-  <si>
-    <t>07.06.202617</t>
-  </si>
-  <si>
-    <t>07.06.202618</t>
-  </si>
-  <si>
-    <t>07.06.202619</t>
-  </si>
-  <si>
-    <t>07.06.202620</t>
-  </si>
-  <si>
-    <t>07.06.202621</t>
-  </si>
-  <si>
-    <t>07.06.202622</t>
-  </si>
-  <si>
-    <t>07.06.202623</t>
-  </si>
-  <si>
-    <t>08.06.20261</t>
-  </si>
-  <si>
-    <t>08.06.20262</t>
-  </si>
-  <si>
-    <t>08.06.20263</t>
-  </si>
-  <si>
-    <t>08.06.20264</t>
-  </si>
-  <si>
-    <t>08.06.20265</t>
-  </si>
-  <si>
-    <t>08.06.20266</t>
-  </si>
-  <si>
-    <t>08.06.20267</t>
-  </si>
-  <si>
-    <t>08.06.20268</t>
-  </si>
-  <si>
-    <t>08.06.20269</t>
-  </si>
-  <si>
-    <t>08.06.202610</t>
-  </si>
-  <si>
-    <t>08.06.202611</t>
-  </si>
-  <si>
-    <t>08.06.202612</t>
-  </si>
-  <si>
-    <t>08.06.202613</t>
-  </si>
-  <si>
-    <t>08.06.202614</t>
-  </si>
-  <si>
-    <t>08.06.202615</t>
-  </si>
-  <si>
-    <t>08.06.202616</t>
-  </si>
-  <si>
-    <t>08.06.202617</t>
-  </si>
-  <si>
-    <t>08.06.202618</t>
-  </si>
-  <si>
-    <t>08.06.202619</t>
-  </si>
-  <si>
-    <t>08.06.202620</t>
-  </si>
-  <si>
-    <t>08.06.202621</t>
-  </si>
-  <si>
-    <t>08.06.202622</t>
-  </si>
-  <si>
-    <t>08.06.202623</t>
-  </si>
-  <si>
-    <t>09.06.20261</t>
-  </si>
-  <si>
-    <t>09.06.20262</t>
-  </si>
-  <si>
-    <t>09.06.20263</t>
-  </si>
-  <si>
-    <t>09.06.20264</t>
-  </si>
-  <si>
-    <t>09.06.20265</t>
-  </si>
-  <si>
-    <t>09.06.20266</t>
-  </si>
-  <si>
-    <t>09.06.20267</t>
-  </si>
-  <si>
-    <t>09.06.20268</t>
-  </si>
-  <si>
-    <t>09.06.20269</t>
-  </si>
-  <si>
-    <t>09.06.202610</t>
-  </si>
-  <si>
-    <t>09.06.202611</t>
-  </si>
-  <si>
-    <t>09.06.202612</t>
-  </si>
-  <si>
-    <t>09.06.202613</t>
-  </si>
-  <si>
-    <t>09.06.202614</t>
-  </si>
-  <si>
-    <t>09.06.202615</t>
-  </si>
-  <si>
-    <t>09.06.202616</t>
-  </si>
-  <si>
-    <t>09.06.202617</t>
-  </si>
-  <si>
-    <t>09.06.202618</t>
-  </si>
-  <si>
-    <t>09.06.202619</t>
-  </si>
-  <si>
-    <t>09.06.202620</t>
-  </si>
-  <si>
-    <t>09.06.202621</t>
-  </si>
-  <si>
-    <t>09.06.202622</t>
-  </si>
-  <si>
-    <t>09.06.202623</t>
-  </si>
-  <si>
-    <t>10.06.20261</t>
-  </si>
-  <si>
-    <t>10.06.20262</t>
-  </si>
-  <si>
-    <t>10.06.20263</t>
-  </si>
-  <si>
-    <t>10.06.20264</t>
-  </si>
-  <si>
-    <t>10.06.20265</t>
-  </si>
-  <si>
-    <t>10.06.20266</t>
-  </si>
-  <si>
-    <t>10.06.20267</t>
-  </si>
-  <si>
-    <t>10.06.20268</t>
-  </si>
-  <si>
-    <t>10.06.20269</t>
-  </si>
-  <si>
-    <t>10.06.202610</t>
-  </si>
-  <si>
-    <t>10.06.202611</t>
-  </si>
-  <si>
-    <t>10.06.202612</t>
-  </si>
-  <si>
-    <t>10.06.202613</t>
-  </si>
-  <si>
-    <t>10.06.202614</t>
-  </si>
-  <si>
-    <t>10.06.202615</t>
-  </si>
-  <si>
-    <t>10.06.202616</t>
-  </si>
-  <si>
-    <t>10.06.202617</t>
-  </si>
-  <si>
-    <t>10.06.202618</t>
-  </si>
-  <si>
-    <t>10.06.202619</t>
-  </si>
-  <si>
-    <t>10.06.202620</t>
-  </si>
-  <si>
-    <t>10.06.202621</t>
-  </si>
-  <si>
-    <t>10.06.202622</t>
-  </si>
-  <si>
-    <t>10.06.202623</t>
-  </si>
-  <si>
-    <t>11.06.20261</t>
-  </si>
-  <si>
-    <t>11.06.20262</t>
-  </si>
-  <si>
-    <t>11.06.20263</t>
-  </si>
-  <si>
-    <t>11.06.20264</t>
-  </si>
-  <si>
-    <t>11.06.20265</t>
-  </si>
-  <si>
-    <t>11.06.20266</t>
-  </si>
-  <si>
-    <t>11.06.20267</t>
-  </si>
-  <si>
-    <t>11.06.20268</t>
-  </si>
-  <si>
-    <t>11.06.20269</t>
-  </si>
-  <si>
-    <t>11.06.202610</t>
-  </si>
-  <si>
-    <t>11.06.202611</t>
-  </si>
-  <si>
-    <t>11.06.202612</t>
-  </si>
-  <si>
-    <t>11.06.202613</t>
-  </si>
-  <si>
-    <t>11.06.202614</t>
-  </si>
-  <si>
-    <t>11.06.202615</t>
+    <t>16.07.202617</t>
+  </si>
+  <si>
+    <t>16.07.202618</t>
+  </si>
+  <si>
+    <t>16.07.202619</t>
+  </si>
+  <si>
+    <t>16.07.202620</t>
+  </si>
+  <si>
+    <t>16.07.202621</t>
+  </si>
+  <si>
+    <t>16.07.202622</t>
+  </si>
+  <si>
+    <t>16.07.202623</t>
+  </si>
+  <si>
+    <t>17.07.20261</t>
+  </si>
+  <si>
+    <t>17.07.20262</t>
+  </si>
+  <si>
+    <t>17.07.20263</t>
+  </si>
+  <si>
+    <t>17.07.20264</t>
+  </si>
+  <si>
+    <t>17.07.20265</t>
+  </si>
+  <si>
+    <t>17.07.20266</t>
+  </si>
+  <si>
+    <t>17.07.20267</t>
+  </si>
+  <si>
+    <t>17.07.20268</t>
+  </si>
+  <si>
+    <t>17.07.20269</t>
+  </si>
+  <si>
+    <t>17.07.202610</t>
+  </si>
+  <si>
+    <t>17.07.202611</t>
+  </si>
+  <si>
+    <t>17.07.202612</t>
+  </si>
+  <si>
+    <t>17.07.202613</t>
+  </si>
+  <si>
+    <t>17.07.202614</t>
+  </si>
+  <si>
+    <t>17.07.202615</t>
+  </si>
+  <si>
+    <t>17.07.202616</t>
+  </si>
+  <si>
+    <t>17.07.202617</t>
+  </si>
+  <si>
+    <t>17.07.202618</t>
+  </si>
+  <si>
+    <t>17.07.202619</t>
+  </si>
+  <si>
+    <t>17.07.202620</t>
+  </si>
+  <si>
+    <t>17.07.202621</t>
+  </si>
+  <si>
+    <t>17.07.202622</t>
+  </si>
+  <si>
+    <t>17.07.202623</t>
+  </si>
+  <si>
+    <t>18.07.20261</t>
+  </si>
+  <si>
+    <t>18.07.20262</t>
+  </si>
+  <si>
+    <t>18.07.20263</t>
+  </si>
+  <si>
+    <t>18.07.20264</t>
+  </si>
+  <si>
+    <t>18.07.20265</t>
+  </si>
+  <si>
+    <t>18.07.20266</t>
+  </si>
+  <si>
+    <t>18.07.20267</t>
+  </si>
+  <si>
+    <t>18.07.20268</t>
+  </si>
+  <si>
+    <t>18.07.20269</t>
+  </si>
+  <si>
+    <t>18.07.202610</t>
+  </si>
+  <si>
+    <t>18.07.202611</t>
+  </si>
+  <si>
+    <t>18.07.202612</t>
+  </si>
+  <si>
+    <t>18.07.202613</t>
+  </si>
+  <si>
+    <t>18.07.202614</t>
+  </si>
+  <si>
+    <t>18.07.202615</t>
+  </si>
+  <si>
+    <t>18.07.202616</t>
+  </si>
+  <si>
+    <t>18.07.202617</t>
+  </si>
+  <si>
+    <t>18.07.202618</t>
+  </si>
+  <si>
+    <t>18.07.202619</t>
+  </si>
+  <si>
+    <t>18.07.202620</t>
+  </si>
+  <si>
+    <t>18.07.202621</t>
+  </si>
+  <si>
+    <t>18.07.202622</t>
+  </si>
+  <si>
+    <t>18.07.202623</t>
+  </si>
+  <si>
+    <t>19.07.20261</t>
+  </si>
+  <si>
+    <t>19.07.20262</t>
+  </si>
+  <si>
+    <t>19.07.20263</t>
+  </si>
+  <si>
+    <t>19.07.20264</t>
+  </si>
+  <si>
+    <t>19.07.20265</t>
+  </si>
+  <si>
+    <t>19.07.20266</t>
+  </si>
+  <si>
+    <t>19.07.20267</t>
+  </si>
+  <si>
+    <t>19.07.20268</t>
+  </si>
+  <si>
+    <t>19.07.20269</t>
+  </si>
+  <si>
+    <t>19.07.202610</t>
+  </si>
+  <si>
+    <t>19.07.202611</t>
+  </si>
+  <si>
+    <t>19.07.202612</t>
+  </si>
+  <si>
+    <t>19.07.202613</t>
+  </si>
+  <si>
+    <t>19.07.202614</t>
+  </si>
+  <si>
+    <t>19.07.202615</t>
+  </si>
+  <si>
+    <t>19.07.202616</t>
+  </si>
+  <si>
+    <t>19.07.202617</t>
+  </si>
+  <si>
+    <t>19.07.202618</t>
+  </si>
+  <si>
+    <t>19.07.202619</t>
+  </si>
+  <si>
+    <t>19.07.202620</t>
+  </si>
+  <si>
+    <t>19.07.202621</t>
+  </si>
+  <si>
+    <t>19.07.202622</t>
+  </si>
+  <si>
+    <t>19.07.202623</t>
+  </si>
+  <si>
+    <t>20.07.20261</t>
+  </si>
+  <si>
+    <t>20.07.20262</t>
+  </si>
+  <si>
+    <t>20.07.20263</t>
+  </si>
+  <si>
+    <t>20.07.20264</t>
+  </si>
+  <si>
+    <t>20.07.20265</t>
+  </si>
+  <si>
+    <t>20.07.20266</t>
+  </si>
+  <si>
+    <t>20.07.20267</t>
+  </si>
+  <si>
+    <t>20.07.20268</t>
+  </si>
+  <si>
+    <t>20.07.20269</t>
+  </si>
+  <si>
+    <t>20.07.202610</t>
+  </si>
+  <si>
+    <t>20.07.202611</t>
+  </si>
+  <si>
+    <t>20.07.202612</t>
+  </si>
+  <si>
+    <t>20.07.202613</t>
+  </si>
+  <si>
+    <t>20.07.202614</t>
+  </si>
+  <si>
+    <t>20.07.202615</t>
+  </si>
+  <si>
+    <t>20.07.202616</t>
+  </si>
+  <si>
+    <t>20.07.202617</t>
+  </si>
+  <si>
+    <t>20.07.202618</t>
+  </si>
+  <si>
+    <t>20.07.202619</t>
+  </si>
+  <si>
+    <t>20.07.202620</t>
+  </si>
+  <si>
+    <t>20.07.202621</t>
+  </si>
+  <si>
+    <t>20.07.202622</t>
+  </si>
+  <si>
+    <t>20.07.202623</t>
+  </si>
+  <si>
+    <t>21.07.20261</t>
+  </si>
+  <si>
+    <t>21.07.20262</t>
+  </si>
+  <si>
+    <t>21.07.20263</t>
+  </si>
+  <si>
+    <t>21.07.20264</t>
+  </si>
+  <si>
+    <t>21.07.20265</t>
+  </si>
+  <si>
+    <t>21.07.20266</t>
+  </si>
+  <si>
+    <t>21.07.20267</t>
+  </si>
+  <si>
+    <t>21.07.20268</t>
+  </si>
+  <si>
+    <t>21.07.20269</t>
+  </si>
+  <si>
+    <t>21.07.202610</t>
+  </si>
+  <si>
+    <t>21.07.202611</t>
+  </si>
+  <si>
+    <t>21.07.202612</t>
+  </si>
+  <si>
+    <t>21.07.202613</t>
+  </si>
+  <si>
+    <t>21.07.202614</t>
+  </si>
+  <si>
+    <t>21.07.202615</t>
+  </si>
+  <si>
+    <t>21.07.202616</t>
+  </si>
+  <si>
+    <t>21.07.202617</t>
+  </si>
+  <si>
+    <t>21.07.202618</t>
+  </si>
+  <si>
+    <t>21.07.202619</t>
+  </si>
+  <si>
+    <t>21.07.202620</t>
+  </si>
+  <si>
+    <t>21.07.202621</t>
+  </si>
+  <si>
+    <t>21.07.202622</t>
+  </si>
+  <si>
+    <t>21.07.202623</t>
+  </si>
+  <si>
+    <t>22.07.20261</t>
+  </si>
+  <si>
+    <t>22.07.20262</t>
+  </si>
+  <si>
+    <t>22.07.20263</t>
+  </si>
+  <si>
+    <t>22.07.20264</t>
+  </si>
+  <si>
+    <t>22.07.20265</t>
+  </si>
+  <si>
+    <t>22.07.20266</t>
+  </si>
+  <si>
+    <t>22.07.20267</t>
+  </si>
+  <si>
+    <t>22.07.20268</t>
+  </si>
+  <si>
+    <t>22.07.20269</t>
+  </si>
+  <si>
+    <t>22.07.202610</t>
+  </si>
+  <si>
+    <t>22.07.202611</t>
+  </si>
+  <si>
+    <t>22.07.202612</t>
+  </si>
+  <si>
+    <t>22.07.202613</t>
+  </si>
+  <si>
+    <t>22.07.202614</t>
+  </si>
+  <si>
+    <t>22.07.202615</t>
+  </si>
+  <si>
+    <t>22.07.202616</t>
+  </si>
+  <si>
+    <t>22.07.202617</t>
+  </si>
+  <si>
+    <t>22.07.202618</t>
+  </si>
+  <si>
+    <t>22.07.202619</t>
+  </si>
+  <si>
+    <t>22.07.202620</t>
+  </si>
+  <si>
+    <t>22.07.202621</t>
+  </si>
+  <si>
+    <t>22.07.202622</t>
+  </si>
+  <si>
+    <t>22.07.202623</t>
+  </si>
+  <si>
+    <t>23.07.20261</t>
+  </si>
+  <si>
+    <t>23.07.20262</t>
+  </si>
+  <si>
+    <t>23.07.20263</t>
+  </si>
+  <si>
+    <t>23.07.20264</t>
+  </si>
+  <si>
+    <t>23.07.20265</t>
+  </si>
+  <si>
+    <t>23.07.20266</t>
+  </si>
+  <si>
+    <t>23.07.20267</t>
+  </si>
+  <si>
+    <t>23.07.20268</t>
+  </si>
+  <si>
+    <t>23.07.20269</t>
+  </si>
+  <si>
+    <t>23.07.202610</t>
+  </si>
+  <si>
+    <t>23.07.202611</t>
+  </si>
+  <si>
+    <t>23.07.202612</t>
+  </si>
+  <si>
+    <t>23.07.202613</t>
+  </si>
+  <si>
+    <t>23.07.202614</t>
+  </si>
+  <si>
+    <t>23.07.202615</t>
+  </si>
+  <si>
+    <t>23.07.202616</t>
   </si>
 </sst>
 </file>
@@ -907,10 +907,10 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46177</v>
+        <v>46219</v>
       </c>
       <c r="B2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -924,10 +924,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46177</v>
+        <v>46219</v>
       </c>
       <c r="B3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -947,19 +947,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46177</v>
+        <v>46219</v>
       </c>
       <c r="B4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4">
-        <v>452</v>
+        <v>357</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>11.5</v>
+        <v>3.1</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -970,22 +970,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46177</v>
+        <v>46219</v>
       </c>
       <c r="B5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>45.6</v>
+        <v>13.4</v>
       </c>
       <c r="F5">
-        <v>1.326</v>
+        <v>0.839</v>
       </c>
       <c r="G5" t="s">
         <v>9</v>
@@ -993,22 +993,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46177</v>
+        <v>46219</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>38.2</v>
+        <v>19.7</v>
       </c>
       <c r="F6">
-        <v>0.514</v>
+        <v>0.273</v>
       </c>
       <c r="G6" t="s">
         <v>10</v>
@@ -1016,22 +1016,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46177</v>
+        <v>46219</v>
       </c>
       <c r="B7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E7">
-        <v>38.5</v>
+        <v>19.5</v>
       </c>
       <c r="F7">
-        <v>0.239</v>
+        <v>0.066</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
@@ -1039,22 +1039,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46177</v>
+        <v>46219</v>
       </c>
       <c r="B8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E8">
-        <v>33</v>
+        <v>21.1</v>
       </c>
       <c r="F8">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G8" t="s">
         <v>12</v>
@@ -1062,19 +1062,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46177</v>
+        <v>46219</v>
       </c>
       <c r="B9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E9">
-        <v>29</v>
+        <v>21.1</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1085,59 +1085,59 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46177</v>
+        <v>46220</v>
       </c>
       <c r="B10">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E10">
-        <v>27.4</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
-        <v>14</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E11">
-        <v>26.7</v>
+        <v>10.3</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E12">
-        <v>25.9</v>
+        <v>8.6</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1148,19 +1148,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E13">
-        <v>25.9</v>
+        <v>7.7</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1171,19 +1171,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E14">
-        <v>25.1</v>
+        <v>7.7</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1194,19 +1194,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E15">
-        <v>25.1</v>
+        <v>6.9</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1217,19 +1217,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>55</v>
+      </c>
+      <c r="D16">
+        <v>17</v>
+      </c>
+      <c r="E16">
         <v>5</v>
-      </c>
-      <c r="C16">
-        <v>3</v>
-      </c>
-      <c r="D16">
-        <v>13</v>
-      </c>
-      <c r="E16">
-        <v>26.7</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1240,22 +1240,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17">
-        <v>58</v>
+        <v>192</v>
       </c>
       <c r="D17">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E17">
-        <v>27.9</v>
+        <v>3.2</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="G17" t="s">
         <v>20</v>
@@ -1263,22 +1263,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18">
-        <v>177</v>
+        <v>358</v>
       </c>
       <c r="D18">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E18">
-        <v>23.4</v>
+        <v>1.9</v>
       </c>
       <c r="F18">
-        <v>0.091</v>
+        <v>0.364</v>
       </c>
       <c r="G18" t="s">
         <v>21</v>
@@ -1286,22 +1286,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19">
-        <v>325</v>
+        <v>527</v>
       </c>
       <c r="D19">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E19">
-        <v>18.9</v>
+        <v>0.6</v>
       </c>
       <c r="F19">
-        <v>0.398</v>
+        <v>1.009</v>
       </c>
       <c r="G19" t="s">
         <v>22</v>
@@ -1309,22 +1309,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C20">
-        <v>460</v>
+        <v>673</v>
       </c>
       <c r="D20">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E20">
-        <v>18.6</v>
+        <v>0.6</v>
       </c>
       <c r="F20">
-        <v>0.832</v>
+        <v>1.777</v>
       </c>
       <c r="G20" t="s">
         <v>23</v>
@@ -1332,22 +1332,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B21">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21">
-        <v>574</v>
+        <v>780</v>
       </c>
       <c r="D21">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E21">
-        <v>19.3</v>
+        <v>1.6</v>
       </c>
       <c r="F21">
-        <v>1.493</v>
+        <v>2.373</v>
       </c>
       <c r="G21" t="s">
         <v>24</v>
@@ -1355,22 +1355,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B22">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C22">
-        <v>668</v>
+        <v>836</v>
       </c>
       <c r="D22">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E22">
-        <v>18.6</v>
+        <v>3.5</v>
       </c>
       <c r="F22">
-        <v>1.924</v>
+        <v>2.694</v>
       </c>
       <c r="G22" t="s">
         <v>25</v>
@@ -1378,22 +1378,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B23">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C23">
-        <v>727</v>
+        <v>827</v>
       </c>
       <c r="D23">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E23">
-        <v>18</v>
+        <v>7.5</v>
       </c>
       <c r="F23">
-        <v>2.421</v>
+        <v>2.873</v>
       </c>
       <c r="G23" t="s">
         <v>26</v>
@@ -1401,22 +1401,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C24">
-        <v>743</v>
+        <v>766</v>
       </c>
       <c r="D24">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E24">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F24">
-        <v>2.591</v>
+        <v>2.791</v>
       </c>
       <c r="G24" t="s">
         <v>27</v>
@@ -1424,22 +1424,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B25">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C25">
-        <v>699</v>
+        <v>678</v>
       </c>
       <c r="D25">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E25">
-        <v>20</v>
+        <v>15.1</v>
       </c>
       <c r="F25">
-        <v>2.638</v>
+        <v>2.508</v>
       </c>
       <c r="G25" t="s">
         <v>28</v>
@@ -1447,22 +1447,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B26">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C26">
-        <v>608</v>
+        <v>567</v>
       </c>
       <c r="D26">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E26">
-        <v>23.6</v>
+        <v>17.4</v>
       </c>
       <c r="F26">
-        <v>2.459</v>
+        <v>2.156</v>
       </c>
       <c r="G26" t="s">
         <v>29</v>
@@ -1470,22 +1470,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B27">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C27">
         <v>444</v>
       </c>
       <c r="D27">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E27">
-        <v>34.5</v>
+        <v>17.7</v>
       </c>
       <c r="F27">
-        <v>1.983</v>
+        <v>1.622</v>
       </c>
       <c r="G27" t="s">
         <v>30</v>
@@ -1493,22 +1493,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B28">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C28">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="D28">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E28">
-        <v>43.2</v>
+        <v>14.2</v>
       </c>
       <c r="F28">
-        <v>1.579</v>
+        <v>1.18</v>
       </c>
       <c r="G28" t="s">
         <v>31</v>
@@ -1516,22 +1516,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B29">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C29">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="D29">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E29">
-        <v>41.3</v>
+        <v>9.9</v>
       </c>
       <c r="F29">
-        <v>1.061</v>
+        <v>0.787</v>
       </c>
       <c r="G29" t="s">
         <v>32</v>
@@ -1539,22 +1539,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B30">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C30">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="D30">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E30">
-        <v>38.5</v>
+        <v>7.6</v>
       </c>
       <c r="F30">
-        <v>0.588</v>
+        <v>0.303</v>
       </c>
       <c r="G30" t="s">
         <v>33</v>
@@ -1562,22 +1562,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B31">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C31">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E31">
-        <v>41.6</v>
+        <v>6.9</v>
       </c>
       <c r="F31">
-        <v>0.266</v>
+        <v>0.061</v>
       </c>
       <c r="G31" t="s">
         <v>34</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B32">
+        <v>22</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
         <v>21</v>
       </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="D32">
-        <v>18</v>
-      </c>
       <c r="E32">
-        <v>41.3</v>
+        <v>8.6</v>
       </c>
       <c r="F32">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="G32" t="s">
         <v>35</v>
@@ -1608,19 +1608,19 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="B33">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E33">
-        <v>39.9</v>
+        <v>10.3</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1631,59 +1631,59 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46178</v>
+        <v>46221</v>
       </c>
       <c r="B34">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E34">
-        <v>39.9</v>
-      </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="G34" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E35">
-        <v>40.6</v>
+        <v>13.7</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E36">
-        <v>39.2</v>
+        <v>16.2</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1694,19 +1694,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E37">
-        <v>38.5</v>
+        <v>18.7</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1717,19 +1717,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E38">
-        <v>39.2</v>
+        <v>20.3</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -1740,19 +1740,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E39">
-        <v>39.9</v>
+        <v>21.9</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1763,19 +1763,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D40">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E40">
-        <v>40.6</v>
+        <v>27.1</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C41">
-        <v>51</v>
+        <v>140</v>
       </c>
       <c r="D41">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E41">
-        <v>40.6</v>
+        <v>28.3</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G41" t="s">
         <v>43</v>
@@ -1809,22 +1809,22 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C42">
-        <v>140</v>
+        <v>266</v>
       </c>
       <c r="D42">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E42">
-        <v>40.7</v>
+        <v>26.4</v>
       </c>
       <c r="F42">
-        <v>0.07199999999999999</v>
+        <v>0.365</v>
       </c>
       <c r="G42" t="s">
         <v>44</v>
@@ -1832,22 +1832,22 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C43">
-        <v>228</v>
+        <v>408</v>
       </c>
       <c r="D43">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E43">
-        <v>44</v>
+        <v>22.4</v>
       </c>
       <c r="F43">
-        <v>0.405</v>
+        <v>0.84</v>
       </c>
       <c r="G43" t="s">
         <v>45</v>
@@ -1855,22 +1855,22 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B44">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C44">
-        <v>330</v>
+        <v>541</v>
       </c>
       <c r="D44">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E44">
-        <v>42.4</v>
+        <v>18.9</v>
       </c>
       <c r="F44">
-        <v>0.838</v>
+        <v>1.418</v>
       </c>
       <c r="G44" t="s">
         <v>46</v>
@@ -1878,22 +1878,22 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B45">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C45">
-        <v>434</v>
+        <v>648</v>
       </c>
       <c r="D45">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E45">
-        <v>39.4</v>
+        <v>16.6</v>
       </c>
       <c r="F45">
-        <v>1.228</v>
+        <v>1.792</v>
       </c>
       <c r="G45" t="s">
         <v>47</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B46">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C46">
-        <v>500</v>
+        <v>740</v>
       </c>
       <c r="D46">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E46">
-        <v>39.6</v>
+        <v>12.5</v>
       </c>
       <c r="F46">
-        <v>1.563</v>
+        <v>2.252</v>
       </c>
       <c r="G46" t="s">
         <v>48</v>
@@ -1924,22 +1924,22 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B47">
+        <v>13</v>
+      </c>
+      <c r="C47">
+        <v>763</v>
+      </c>
+      <c r="D47">
+        <v>31</v>
+      </c>
+      <c r="E47">
         <v>12</v>
       </c>
-      <c r="C47">
-        <v>534</v>
-      </c>
-      <c r="D47">
-        <v>23</v>
-      </c>
-      <c r="E47">
-        <v>40.5</v>
-      </c>
       <c r="F47">
-        <v>1.729</v>
+        <v>2.479</v>
       </c>
       <c r="G47" t="s">
         <v>49</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B48">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C48">
-        <v>574</v>
+        <v>662</v>
       </c>
       <c r="D48">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E48">
-        <v>37.5</v>
+        <v>21.5</v>
       </c>
       <c r="F48">
-        <v>1.827</v>
+        <v>2.557</v>
       </c>
       <c r="G48" t="s">
         <v>50</v>
@@ -1970,22 +1970,22 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B49">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C49">
-        <v>613</v>
+        <v>524</v>
       </c>
       <c r="D49">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E49">
-        <v>31</v>
+        <v>31.6</v>
       </c>
       <c r="F49">
-        <v>2.067</v>
+        <v>2.175</v>
       </c>
       <c r="G49" t="s">
         <v>51</v>
@@ -1993,22 +1993,22 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B50">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C50">
-        <v>585</v>
+        <v>439</v>
       </c>
       <c r="D50">
         <v>25</v>
       </c>
       <c r="E50">
-        <v>27.6</v>
+        <v>32</v>
       </c>
       <c r="F50">
-        <v>2.205</v>
+        <v>1.738</v>
       </c>
       <c r="G50" t="s">
         <v>52</v>
@@ -2016,22 +2016,22 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B51">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C51">
-        <v>480</v>
+        <v>372</v>
       </c>
       <c r="D51">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E51">
-        <v>30</v>
+        <v>26.9</v>
       </c>
       <c r="F51">
-        <v>1.911</v>
+        <v>1.583</v>
       </c>
       <c r="G51" t="s">
         <v>53</v>
@@ -2039,22 +2039,22 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B52">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C52">
-        <v>357</v>
+        <v>268</v>
       </c>
       <c r="D52">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E52">
-        <v>33.1</v>
+        <v>24.7</v>
       </c>
       <c r="F52">
-        <v>1.601</v>
+        <v>1.181</v>
       </c>
       <c r="G52" t="s">
         <v>54</v>
@@ -2062,22 +2062,22 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B53">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C53">
-        <v>226</v>
+        <v>141</v>
       </c>
       <c r="D53">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E53">
-        <v>38.7</v>
+        <v>26.2</v>
       </c>
       <c r="F53">
-        <v>1.093</v>
+        <v>0.649</v>
       </c>
       <c r="G53" t="s">
         <v>55</v>
@@ -2085,22 +2085,22 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B54">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C54">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="D54">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E54">
-        <v>44.8</v>
+        <v>30</v>
       </c>
       <c r="F54">
-        <v>0.618</v>
+        <v>0.309</v>
       </c>
       <c r="G54" t="s">
         <v>56</v>
@@ -2108,22 +2108,22 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B55">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C55">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E55">
-        <v>48.1</v>
+        <v>30.5</v>
       </c>
       <c r="F55">
-        <v>0.297</v>
+        <v>0.055</v>
       </c>
       <c r="G55" t="s">
         <v>57</v>
@@ -2131,22 +2131,22 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B56">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E56">
-        <v>44</v>
+        <v>29.7</v>
       </c>
       <c r="F56">
-        <v>0.056</v>
+        <v>0</v>
       </c>
       <c r="G56" t="s">
         <v>58</v>
@@ -2154,19 +2154,19 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46179</v>
+        <v>46221</v>
       </c>
       <c r="B57">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E57">
-        <v>42</v>
+        <v>28.2</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -2177,59 +2177,59 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46179</v>
+        <v>46222</v>
       </c>
       <c r="B58">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E58">
-        <v>43.4</v>
-      </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58" t="s">
-        <v>60</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E59">
-        <v>47.3</v>
+        <v>32</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E60">
-        <v>50.6</v>
+        <v>31.2</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2240,19 +2240,19 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E61">
-        <v>50.6</v>
+        <v>34.9</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -2263,19 +2263,19 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E62">
-        <v>51.2</v>
+        <v>41.3</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -2286,19 +2286,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E63">
-        <v>52.4</v>
+        <v>43.4</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -2309,19 +2309,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D64">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E64">
-        <v>52.4</v>
+        <v>42.9</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2332,22 +2332,22 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C65">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="D65">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E65">
-        <v>53.2</v>
+        <v>37.5</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="G65" t="s">
         <v>66</v>
@@ -2355,22 +2355,22 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B66">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C66">
-        <v>107</v>
+        <v>235</v>
       </c>
       <c r="D66">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E66">
-        <v>54</v>
+        <v>32.4</v>
       </c>
       <c r="F66">
-        <v>0.061</v>
+        <v>0.295</v>
       </c>
       <c r="G66" t="s">
         <v>67</v>
@@ -2378,22 +2378,22 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B67">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C67">
-        <v>178</v>
+        <v>354</v>
       </c>
       <c r="D67">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E67">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F67">
-        <v>0.236</v>
+        <v>0.773</v>
       </c>
       <c r="G67" t="s">
         <v>68</v>
@@ -2401,22 +2401,22 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B68">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C68">
-        <v>288</v>
+        <v>448</v>
       </c>
       <c r="D68">
         <v>21</v>
       </c>
       <c r="E68">
-        <v>49.4</v>
+        <v>32</v>
       </c>
       <c r="F68">
-        <v>0.704</v>
+        <v>1.223</v>
       </c>
       <c r="G68" t="s">
         <v>69</v>
@@ -2424,22 +2424,22 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B69">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C69">
-        <v>441</v>
+        <v>489</v>
       </c>
       <c r="D69">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E69">
-        <v>37.9</v>
+        <v>36.7</v>
       </c>
       <c r="F69">
-        <v>0.962</v>
+        <v>1.551</v>
       </c>
       <c r="G69" t="s">
         <v>70</v>
@@ -2447,22 +2447,22 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B70">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C70">
-        <v>588</v>
+        <v>503</v>
       </c>
       <c r="D70">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E70">
-        <v>28.1</v>
+        <v>40.5</v>
       </c>
       <c r="F70">
-        <v>1.575</v>
+        <v>1.698</v>
       </c>
       <c r="G70" t="s">
         <v>71</v>
@@ -2470,22 +2470,22 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B71">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C71">
-        <v>707</v>
+        <v>536</v>
       </c>
       <c r="D71">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E71">
-        <v>20.5</v>
+        <v>38.5</v>
       </c>
       <c r="F71">
-        <v>2.076</v>
+        <v>1.756</v>
       </c>
       <c r="G71" t="s">
         <v>72</v>
@@ -2493,22 +2493,22 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B72">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C72">
-        <v>785</v>
+        <v>560</v>
       </c>
       <c r="D72">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E72">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F72">
-        <v>2.492</v>
+        <v>1.825</v>
       </c>
       <c r="G72" t="s">
         <v>73</v>
@@ -2516,22 +2516,22 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B73">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C73">
-        <v>766</v>
+        <v>549</v>
       </c>
       <c r="D73">
         <v>25</v>
       </c>
       <c r="E73">
-        <v>13.5</v>
+        <v>29.6</v>
       </c>
       <c r="F73">
-        <v>2.809</v>
+        <v>1.979</v>
       </c>
       <c r="G73" t="s">
         <v>74</v>
@@ -2539,22 +2539,22 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B74">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C74">
-        <v>704</v>
+        <v>489</v>
       </c>
       <c r="D74">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E74">
-        <v>13.1</v>
+        <v>27</v>
       </c>
       <c r="F74">
-        <v>2.698</v>
+        <v>1.819</v>
       </c>
       <c r="G74" t="s">
         <v>75</v>
@@ -2562,22 +2562,22 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B75">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C75">
-        <v>606</v>
+        <v>361</v>
       </c>
       <c r="D75">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E75">
-        <v>12.8</v>
+        <v>31.5</v>
       </c>
       <c r="F75">
-        <v>2.282</v>
+        <v>1.717</v>
       </c>
       <c r="G75" t="s">
         <v>76</v>
@@ -2585,22 +2585,22 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B76">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C76">
-        <v>461</v>
+        <v>241</v>
       </c>
       <c r="D76">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E76">
-        <v>15.7</v>
+        <v>33.2</v>
       </c>
       <c r="F76">
-        <v>1.94</v>
+        <v>1.085</v>
       </c>
       <c r="G76" t="s">
         <v>77</v>
@@ -2608,22 +2608,22 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B77">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C77">
-        <v>315</v>
+        <v>135</v>
       </c>
       <c r="D77">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E77">
-        <v>17.1</v>
+        <v>32.4</v>
       </c>
       <c r="F77">
-        <v>1.339</v>
+        <v>0.606</v>
       </c>
       <c r="G77" t="s">
         <v>78</v>
@@ -2631,22 +2631,22 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B78">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C78">
-        <v>177</v>
+        <v>36</v>
       </c>
       <c r="D78">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E78">
-        <v>16.7</v>
+        <v>38</v>
       </c>
       <c r="F78">
-        <v>0.862</v>
+        <v>0.382</v>
       </c>
       <c r="G78" t="s">
         <v>79</v>
@@ -2654,22 +2654,22 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B79">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C79">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E79">
-        <v>14.3</v>
+        <v>35.7</v>
       </c>
       <c r="F79">
-        <v>0.276</v>
+        <v>0.055</v>
       </c>
       <c r="G79" t="s">
         <v>80</v>
@@ -2677,22 +2677,22 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B80">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80">
         <v>19</v>
       </c>
       <c r="E80">
-        <v>9.5</v>
+        <v>29.7</v>
       </c>
       <c r="F80">
-        <v>0.076</v>
+        <v>0</v>
       </c>
       <c r="G80" t="s">
         <v>81</v>
@@ -2700,10 +2700,10 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46180</v>
+        <v>46222</v>
       </c>
       <c r="B81">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2712,7 +2712,7 @@
         <v>18</v>
       </c>
       <c r="E81">
-        <v>6.9</v>
+        <v>26.7</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -2723,59 +2723,59 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46180</v>
+        <v>46223</v>
       </c>
       <c r="B82">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E82">
-        <v>6</v>
-      </c>
-      <c r="F82">
-        <v>0</v>
-      </c>
-      <c r="G82" t="s">
-        <v>83</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E83">
-        <v>5.1</v>
+        <v>25.9</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E84">
-        <v>4.2</v>
+        <v>32</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -2786,19 +2786,19 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E85">
-        <v>6</v>
+        <v>33.5</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -2809,19 +2809,19 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B86">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E86">
-        <v>6.9</v>
+        <v>33.5</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -2832,19 +2832,19 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B87">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E87">
-        <v>6</v>
+        <v>38.5</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -2855,19 +2855,19 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B88">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C88">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="D88">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E88">
-        <v>6.9</v>
+        <v>38.2</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -2878,22 +2878,22 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B89">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C89">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="D89">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E89">
-        <v>6.6</v>
+        <v>27.9</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="G89" t="s">
         <v>89</v>
@@ -2901,22 +2901,22 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B90">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C90">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D90">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E90">
-        <v>4.3</v>
+        <v>29.1</v>
       </c>
       <c r="F90">
-        <v>0.097</v>
+        <v>0.359</v>
       </c>
       <c r="G90" t="s">
         <v>90</v>
@@ -2924,22 +2924,22 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B91">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C91">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="D91">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E91">
-        <v>5.1</v>
+        <v>26</v>
       </c>
       <c r="F91">
-        <v>0.521</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="G91" t="s">
         <v>91</v>
@@ -2947,22 +2947,22 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B92">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C92">
-        <v>556</v>
+        <v>511</v>
       </c>
       <c r="D92">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E92">
-        <v>5.3</v>
+        <v>22.4</v>
       </c>
       <c r="F92">
-        <v>1.136</v>
+        <v>1.246</v>
       </c>
       <c r="G92" t="s">
         <v>92</v>
@@ -2970,22 +2970,22 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B93">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C93">
-        <v>697</v>
+        <v>528</v>
       </c>
       <c r="D93">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E93">
-        <v>4.7</v>
+        <v>31.7</v>
       </c>
       <c r="F93">
-        <v>1.856</v>
+        <v>1.757</v>
       </c>
       <c r="G93" t="s">
         <v>93</v>
@@ -2993,22 +2993,22 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B94">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C94">
-        <v>773</v>
+        <v>520</v>
       </c>
       <c r="D94">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E94">
-        <v>8.1</v>
+        <v>38.5</v>
       </c>
       <c r="F94">
-        <v>2.417</v>
+        <v>1.846</v>
       </c>
       <c r="G94" t="s">
         <v>94</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B95">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C95">
-        <v>828</v>
+        <v>521</v>
       </c>
       <c r="D95">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E95">
-        <v>9</v>
+        <v>40.5</v>
       </c>
       <c r="F95">
-        <v>2.652</v>
+        <v>1.801</v>
       </c>
       <c r="G95" t="s">
         <v>95</v>
@@ -3039,22 +3039,22 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B96">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C96">
-        <v>855</v>
+        <v>543</v>
       </c>
       <c r="D96">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E96">
-        <v>8</v>
+        <v>36.5</v>
       </c>
       <c r="F96">
-        <v>2.971</v>
+        <v>1.822</v>
       </c>
       <c r="G96" t="s">
         <v>96</v>
@@ -3062,22 +3062,22 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B97">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C97">
-        <v>810</v>
+        <v>499</v>
       </c>
       <c r="D97">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E97">
-        <v>10</v>
+        <v>36.2</v>
       </c>
       <c r="F97">
-        <v>2.966</v>
+        <v>1.825</v>
       </c>
       <c r="G97" t="s">
         <v>97</v>
@@ -3085,22 +3085,22 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B98">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C98">
-        <v>730</v>
+        <v>412</v>
       </c>
       <c r="D98">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E98">
-        <v>10.6</v>
+        <v>38</v>
       </c>
       <c r="F98">
-        <v>2.765</v>
+        <v>1.682</v>
       </c>
       <c r="G98" t="s">
         <v>98</v>
@@ -3108,22 +3108,22 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B99">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C99">
-        <v>630</v>
+        <v>367</v>
       </c>
       <c r="D99">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E99">
-        <v>9.199999999999999</v>
+        <v>29.5</v>
       </c>
       <c r="F99">
-        <v>2.368</v>
+        <v>1.388</v>
       </c>
       <c r="G99" t="s">
         <v>99</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B100">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C100">
-        <v>496</v>
+        <v>270</v>
       </c>
       <c r="D100">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E100">
-        <v>8.9</v>
+        <v>25.3</v>
       </c>
       <c r="F100">
-        <v>2.099</v>
+        <v>1.117</v>
       </c>
       <c r="G100" t="s">
         <v>100</v>
@@ -3154,22 +3154,22 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B101">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C101">
-        <v>341</v>
+        <v>144</v>
       </c>
       <c r="D101">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E101">
-        <v>8.699999999999999</v>
+        <v>25.6</v>
       </c>
       <c r="F101">
-        <v>1.45</v>
+        <v>0.646</v>
       </c>
       <c r="G101" t="s">
         <v>101</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B102">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C102">
-        <v>187</v>
+        <v>43</v>
       </c>
       <c r="D102">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E102">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F102">
-        <v>0.8159999999999999</v>
+        <v>0.324</v>
       </c>
       <c r="G102" t="s">
         <v>102</v>
@@ -3200,22 +3200,22 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B103">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C103">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D103">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E103">
-        <v>10.2</v>
+        <v>12</v>
       </c>
       <c r="F103">
-        <v>0.313</v>
+        <v>0.055</v>
       </c>
       <c r="G103" t="s">
         <v>103</v>
@@ -3223,22 +3223,22 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B104">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E104">
         <v>9.5</v>
       </c>
       <c r="F104">
-        <v>0.056</v>
+        <v>0</v>
       </c>
       <c r="G104" t="s">
         <v>104</v>
@@ -3246,19 +3246,19 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46181</v>
+        <v>46223</v>
       </c>
       <c r="B105">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C105">
         <v>0</v>
       </c>
       <c r="D105">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E105">
-        <v>7.7</v>
+        <v>11.2</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -3269,59 +3269,59 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46181</v>
+        <v>46224</v>
       </c>
       <c r="B106">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C106">
         <v>0</v>
       </c>
       <c r="D106">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E106">
-        <v>7.7</v>
-      </c>
-      <c r="F106">
-        <v>0</v>
-      </c>
-      <c r="G106" t="s">
-        <v>106</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C107">
         <v>0</v>
       </c>
       <c r="D107">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E107">
-        <v>6</v>
+        <v>17.9</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C108">
         <v>0</v>
       </c>
       <c r="D108">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E108">
-        <v>4.2</v>
+        <v>21.1</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -3332,19 +3332,19 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B109">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C109">
         <v>0</v>
       </c>
       <c r="D109">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E109">
-        <v>4.2</v>
+        <v>24.3</v>
       </c>
       <c r="F109">
         <v>0</v>
@@ -3355,19 +3355,19 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B110">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C110">
         <v>0</v>
       </c>
       <c r="D110">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E110">
-        <v>3.3</v>
+        <v>31.2</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -3378,19 +3378,19 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B111">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C111">
         <v>0</v>
       </c>
       <c r="D111">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E111">
-        <v>2.4</v>
+        <v>30.5</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -3401,19 +3401,19 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B112">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C112">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D112">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E112">
-        <v>3.3</v>
+        <v>33.8</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -3424,22 +3424,22 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B113">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C113">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="D113">
         <v>15</v>
       </c>
       <c r="E113">
-        <v>3.2</v>
+        <v>30</v>
       </c>
       <c r="F113">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="G113" t="s">
         <v>112</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B114">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C114">
-        <v>229</v>
+        <v>285</v>
       </c>
       <c r="D114">
         <v>17</v>
       </c>
       <c r="E114">
-        <v>1.6</v>
+        <v>19.5</v>
       </c>
       <c r="F114">
-        <v>0.08500000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="G114" t="s">
         <v>113</v>
@@ -3470,22 +3470,22 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B115">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C115">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="D115">
         <v>19</v>
       </c>
       <c r="E115">
-        <v>1.2</v>
+        <v>18.3</v>
       </c>
       <c r="F115">
-        <v>0.458</v>
+        <v>0.874</v>
       </c>
       <c r="G115" t="s">
         <v>114</v>
@@ -3493,22 +3493,22 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B116">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C116">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="D116">
         <v>21</v>
       </c>
       <c r="E116">
-        <v>1.6</v>
+        <v>19.4</v>
       </c>
       <c r="F116">
-        <v>1.129</v>
+        <v>1.484</v>
       </c>
       <c r="G116" t="s">
         <v>115</v>
@@ -3516,22 +3516,22 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B117">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C117">
-        <v>699</v>
+        <v>656</v>
       </c>
       <c r="D117">
         <v>22</v>
       </c>
       <c r="E117">
-        <v>2.1</v>
+        <v>17.1</v>
       </c>
       <c r="F117">
-        <v>1.839</v>
+        <v>1.813</v>
       </c>
       <c r="G117" t="s">
         <v>116</v>
@@ -3539,22 +3539,22 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B118">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C118">
-        <v>803</v>
+        <v>714</v>
       </c>
       <c r="D118">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E118">
-        <v>2.5</v>
+        <v>17.5</v>
       </c>
       <c r="F118">
-        <v>2.462</v>
+        <v>2.359</v>
       </c>
       <c r="G118" t="s">
         <v>117</v>
@@ -3562,22 +3562,22 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B119">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C119">
-        <v>859</v>
+        <v>718</v>
       </c>
       <c r="D119">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E119">
-        <v>3.5</v>
+        <v>19.5</v>
       </c>
       <c r="F119">
-        <v>2.808</v>
+        <v>2.526</v>
       </c>
       <c r="G119" t="s">
         <v>118</v>
@@ -3585,22 +3585,22 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B120">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C120">
-        <v>869</v>
+        <v>693</v>
       </c>
       <c r="D120">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E120">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="F120">
-        <v>2.985</v>
+        <v>2.423</v>
       </c>
       <c r="G120" t="s">
         <v>119</v>
@@ -3608,22 +3608,22 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B121">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C121">
-        <v>831</v>
+        <v>600</v>
       </c>
       <c r="D121">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E121">
-        <v>5.5</v>
+        <v>24.6</v>
       </c>
       <c r="F121">
-        <v>2.929</v>
+        <v>2.434</v>
       </c>
       <c r="G121" t="s">
         <v>120</v>
@@ -3631,22 +3631,22 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B122">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C122">
-        <v>749</v>
+        <v>474</v>
       </c>
       <c r="D122">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E122">
-        <v>6.6</v>
+        <v>30.5</v>
       </c>
       <c r="F122">
-        <v>2.798</v>
+        <v>2.036</v>
       </c>
       <c r="G122" t="s">
         <v>121</v>
@@ -3654,22 +3654,22 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B123">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C123">
-        <v>634</v>
+        <v>353</v>
       </c>
       <c r="D123">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E123">
-        <v>7.2</v>
+        <v>34.1</v>
       </c>
       <c r="F123">
-        <v>2.569</v>
+        <v>1.613</v>
       </c>
       <c r="G123" t="s">
         <v>122</v>
@@ -3677,22 +3677,22 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B124">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C124">
-        <v>492</v>
+        <v>237</v>
       </c>
       <c r="D124">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E124">
-        <v>7.9</v>
+        <v>35.5</v>
       </c>
       <c r="F124">
-        <v>2.109</v>
+        <v>1.126</v>
       </c>
       <c r="G124" t="s">
         <v>123</v>
@@ -3700,22 +3700,22 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B125">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C125">
-        <v>335</v>
+        <v>135</v>
       </c>
       <c r="D125">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E125">
-        <v>8.699999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="F125">
-        <v>1.44</v>
+        <v>0.598</v>
       </c>
       <c r="G125" t="s">
         <v>124</v>
@@ -3723,22 +3723,22 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B126">
+        <v>20</v>
+      </c>
+      <c r="C126">
+        <v>40</v>
+      </c>
+      <c r="D126">
         <v>19</v>
       </c>
-      <c r="C126">
-        <v>179</v>
-      </c>
-      <c r="D126">
-        <v>22</v>
-      </c>
       <c r="E126">
-        <v>10</v>
+        <v>27.8</v>
       </c>
       <c r="F126">
-        <v>0.788</v>
+        <v>0.304</v>
       </c>
       <c r="G126" t="s">
         <v>125</v>
@@ -3746,22 +3746,22 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B127">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C127">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="D127">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E127">
-        <v>12.7</v>
+        <v>24.3</v>
       </c>
       <c r="F127">
-        <v>0.281</v>
+        <v>0.06</v>
       </c>
       <c r="G127" t="s">
         <v>126</v>
@@ -3769,22 +3769,22 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B128">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D128">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E128">
-        <v>12</v>
+        <v>25.1</v>
       </c>
       <c r="F128">
-        <v>0.059</v>
+        <v>0</v>
       </c>
       <c r="G128" t="s">
         <v>127</v>
@@ -3792,10 +3792,10 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46182</v>
+        <v>46224</v>
       </c>
       <c r="B129">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>17</v>
       </c>
       <c r="E129">
-        <v>11.2</v>
+        <v>26.7</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -3815,59 +3815,59 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46182</v>
+        <v>46225</v>
       </c>
       <c r="B130">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C130">
         <v>0</v>
       </c>
       <c r="D130">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E130">
-        <v>11.2</v>
-      </c>
-      <c r="F130">
-        <v>0</v>
-      </c>
-      <c r="G130" t="s">
-        <v>129</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C131">
         <v>0</v>
       </c>
       <c r="D131">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E131">
-        <v>11.2</v>
+        <v>24.3</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+      <c r="G131" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C132">
         <v>0</v>
       </c>
       <c r="D132">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E132">
-        <v>11.2</v>
+        <v>21.9</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -3878,19 +3878,19 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B133">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C133">
         <v>0</v>
       </c>
       <c r="D133">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E133">
-        <v>11.2</v>
+        <v>17.9</v>
       </c>
       <c r="F133">
         <v>0</v>
@@ -3901,19 +3901,19 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B134">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C134">
         <v>0</v>
       </c>
       <c r="D134">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E134">
-        <v>10.3</v>
+        <v>12</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -3924,19 +3924,19 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B135">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C135">
         <v>0</v>
       </c>
       <c r="D135">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E135">
-        <v>10.3</v>
+        <v>6.9</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -3947,19 +3947,19 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B136">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C136">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="D136">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E136">
-        <v>11.2</v>
+        <v>4.2</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -3970,22 +3970,22 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B137">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C137">
-        <v>71</v>
+        <v>180</v>
       </c>
       <c r="D137">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E137">
-        <v>11.5</v>
+        <v>3.2</v>
       </c>
       <c r="F137">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="G137" t="s">
         <v>135</v>
@@ -3993,22 +3993,22 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B138">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C138">
-        <v>203</v>
+        <v>348</v>
       </c>
       <c r="D138">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E138">
-        <v>10.1</v>
+        <v>2.5</v>
       </c>
       <c r="F138">
-        <v>0.08</v>
+        <v>0.379</v>
       </c>
       <c r="G138" t="s">
         <v>136</v>
@@ -4016,22 +4016,22 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B139">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C139">
-        <v>354</v>
+        <v>515</v>
       </c>
       <c r="D139">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E139">
-        <v>9.5</v>
+        <v>2.2</v>
       </c>
       <c r="F139">
-        <v>0.436</v>
+        <v>1.039</v>
       </c>
       <c r="G139" t="s">
         <v>137</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B140">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C140">
-        <v>502</v>
+        <v>656</v>
       </c>
       <c r="D140">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E140">
-        <v>9.4</v>
+        <v>3.2</v>
       </c>
       <c r="F140">
-        <v>0.97</v>
+        <v>1.784</v>
       </c>
       <c r="G140" t="s">
         <v>138</v>
@@ -4062,22 +4062,22 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B141">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C141">
-        <v>635</v>
+        <v>763</v>
       </c>
       <c r="D141">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E141">
-        <v>8.699999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="F141">
-        <v>1.395</v>
+        <v>2.328</v>
       </c>
       <c r="G141" t="s">
         <v>139</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B142">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C142">
-        <v>731</v>
+        <v>833</v>
       </c>
       <c r="D142">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E142">
-        <v>9.1</v>
+        <v>4.5</v>
       </c>
       <c r="F142">
-        <v>1.898</v>
+        <v>2.654</v>
       </c>
       <c r="G142" t="s">
         <v>140</v>
@@ -4108,22 +4108,22 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B143">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C143">
-        <v>774</v>
+        <v>857</v>
       </c>
       <c r="D143">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E143">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F143">
-        <v>2.313</v>
+        <v>2.969</v>
       </c>
       <c r="G143" t="s">
         <v>141</v>
@@ -4131,22 +4131,22 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B144">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C144">
-        <v>773</v>
+        <v>836</v>
       </c>
       <c r="D144">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E144">
-        <v>13.5</v>
+        <v>5</v>
       </c>
       <c r="F144">
-        <v>2.404</v>
+        <v>2.993</v>
       </c>
       <c r="G144" t="s">
         <v>142</v>
@@ -4154,22 +4154,22 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B145">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C145">
-        <v>728</v>
+        <v>753</v>
       </c>
       <c r="D145">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E145">
-        <v>16</v>
+        <v>7.1</v>
       </c>
       <c r="F145">
-        <v>2.553</v>
+        <v>2.86</v>
       </c>
       <c r="G145" t="s">
         <v>143</v>
@@ -4177,22 +4177,22 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B146">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C146">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="D146">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E146">
-        <v>19.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F146">
-        <v>2.524</v>
+        <v>2.586</v>
       </c>
       <c r="G146" t="s">
         <v>144</v>
@@ -4200,22 +4200,22 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B147">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C147">
-        <v>531</v>
+        <v>500</v>
       </c>
       <c r="D147">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E147">
-        <v>21.4</v>
+        <v>8.9</v>
       </c>
       <c r="F147">
-        <v>2.128</v>
+        <v>2.14</v>
       </c>
       <c r="G147" t="s">
         <v>145</v>
@@ -4223,22 +4223,22 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B148">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C148">
-        <v>402</v>
+        <v>351</v>
       </c>
       <c r="D148">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E148">
-        <v>23.9</v>
+        <v>7</v>
       </c>
       <c r="F148">
-        <v>1.759</v>
+        <v>1.427</v>
       </c>
       <c r="G148" t="s">
         <v>146</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B149">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C149">
-        <v>260</v>
+        <v>194</v>
       </c>
       <c r="D149">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E149">
-        <v>28.5</v>
+        <v>5.3</v>
       </c>
       <c r="F149">
-        <v>1.259</v>
+        <v>0.888</v>
       </c>
       <c r="G149" t="s">
         <v>147</v>
@@ -4269,22 +4269,22 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B150">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C150">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="D150">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E150">
-        <v>35.3</v>
+        <v>5</v>
       </c>
       <c r="F150">
-        <v>0.671</v>
+        <v>0.295</v>
       </c>
       <c r="G150" t="s">
         <v>148</v>
@@ -4292,22 +4292,22 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B151">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C151">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D151">
         <v>16</v>
       </c>
       <c r="E151">
-        <v>43.4</v>
+        <v>4.2</v>
       </c>
       <c r="F151">
-        <v>0.277</v>
+        <v>0.053</v>
       </c>
       <c r="G151" t="s">
         <v>149</v>
@@ -4315,22 +4315,22 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B152">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D152">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E152">
-        <v>43.4</v>
+        <v>4.2</v>
       </c>
       <c r="F152">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="G152" t="s">
         <v>150</v>
@@ -4338,19 +4338,19 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46183</v>
+        <v>46225</v>
       </c>
       <c r="B153">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C153">
         <v>0</v>
       </c>
       <c r="D153">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E153">
-        <v>42.7</v>
+        <v>4.2</v>
       </c>
       <c r="F153">
         <v>0</v>
@@ -4361,59 +4361,59 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46183</v>
+        <v>46226</v>
       </c>
       <c r="B154">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C154">
         <v>0</v>
       </c>
       <c r="D154">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E154">
-        <v>42</v>
-      </c>
-      <c r="F154">
-        <v>0</v>
-      </c>
-      <c r="G154" t="s">
-        <v>152</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46184</v>
+        <v>46226</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C155">
         <v>0</v>
       </c>
       <c r="D155">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E155">
-        <v>40.6</v>
+        <v>23.4</v>
+      </c>
+      <c r="F155">
+        <v>0</v>
+      </c>
+      <c r="G155" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46184</v>
+        <v>46226</v>
       </c>
       <c r="B156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C156">
         <v>0</v>
       </c>
       <c r="D156">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E156">
-        <v>37.8</v>
+        <v>32</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -4424,19 +4424,19 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46184</v>
+        <v>46226</v>
       </c>
       <c r="B157">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C157">
         <v>0</v>
       </c>
       <c r="D157">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E157">
-        <v>35.7</v>
+        <v>30.5</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -4447,10 +4447,10 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46184</v>
+        <v>46226</v>
       </c>
       <c r="B158">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -4459,7 +4459,7 @@
         <v>12</v>
       </c>
       <c r="E158">
-        <v>34.9</v>
+        <v>33.5</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -4470,19 +4470,19 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46184</v>
+        <v>46226</v>
       </c>
       <c r="B159">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C159">
         <v>0</v>
       </c>
       <c r="D159">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E159">
-        <v>34.9</v>
+        <v>35.7</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -4493,19 +4493,19 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46184</v>
+        <v>46226</v>
       </c>
       <c r="B160">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C160">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D160">
         <v>12</v>
       </c>
       <c r="E160">
-        <v>33.5</v>
+        <v>35.4</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -4516,22 +4516,22 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46184</v>
+        <v>46226</v>
       </c>
       <c r="B161">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C161">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="D161">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E161">
-        <v>30.8</v>
+        <v>27</v>
       </c>
       <c r="F161">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="G161" t="s">
         <v>158</v>
@@ -4539,22 +4539,22 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46184</v>
+        <v>46226</v>
       </c>
       <c r="B162">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C162">
-        <v>166</v>
+        <v>292</v>
       </c>
       <c r="D162">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E162">
-        <v>26.3</v>
+        <v>19.6</v>
       </c>
       <c r="F162">
-        <v>0.082</v>
+        <v>0.39</v>
       </c>
       <c r="G162" t="s">
         <v>159</v>
@@ -4562,22 +4562,22 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46184</v>
+        <v>46226</v>
       </c>
       <c r="B163">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C163">
-        <v>303</v>
+        <v>446</v>
       </c>
       <c r="D163">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E163">
-        <v>23.1</v>
+        <v>16.2</v>
       </c>
       <c r="F163">
-        <v>0.427</v>
+        <v>1.071</v>
       </c>
       <c r="G163" t="s">
         <v>160</v>
@@ -4585,22 +4585,22 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46184</v>
+        <v>46226</v>
       </c>
       <c r="B164">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C164">
-        <v>446</v>
+        <v>567</v>
       </c>
       <c r="D164">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E164">
-        <v>20.1</v>
+        <v>16.9</v>
       </c>
       <c r="F164">
-        <v>1.012</v>
+        <v>1.669</v>
       </c>
       <c r="G164" t="s">
         <v>161</v>
@@ -4608,22 +4608,22 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46184</v>
+        <v>46226</v>
       </c>
       <c r="B165">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C165">
-        <v>563</v>
+        <v>643</v>
       </c>
       <c r="D165">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E165">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="F165">
-        <v>1.555</v>
+        <v>1.926</v>
       </c>
       <c r="G165" t="s">
         <v>162</v>
@@ -4631,22 +4631,22 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46184</v>
+        <v>46226</v>
       </c>
       <c r="B166">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C166">
-        <v>659</v>
+        <v>677</v>
       </c>
       <c r="D166">
         <v>22</v>
       </c>
       <c r="E166">
-        <v>19.1</v>
+        <v>22.5</v>
       </c>
       <c r="F166">
-        <v>1.919</v>
+        <v>2.258</v>
       </c>
       <c r="G166" t="s">
         <v>163</v>
@@ -4654,22 +4654,22 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46184</v>
+        <v>46226</v>
       </c>
       <c r="B167">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C167">
-        <v>733</v>
+        <v>675</v>
       </c>
       <c r="D167">
         <v>23</v>
       </c>
       <c r="E167">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F167">
-        <v>2.349</v>
+        <v>2.358</v>
       </c>
       <c r="G167" t="s">
         <v>164</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46184</v>
+        <v>46226</v>
       </c>
       <c r="B168">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C168">
-        <v>768</v>
+        <v>626</v>
       </c>
       <c r="D168">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E168">
-        <v>15</v>
+        <v>28.5</v>
       </c>
       <c r="F168">
-        <v>2.644</v>
+        <v>2.356</v>
       </c>
       <c r="G168" t="s">
         <v>165</v>
@@ -4700,22 +4700,22 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46184</v>
+        <v>46226</v>
       </c>
       <c r="B169">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C169">
-        <v>747</v>
+        <v>528</v>
       </c>
       <c r="D169">
         <v>24</v>
       </c>
       <c r="E169">
-        <v>14.5</v>
+        <v>34.2</v>
       </c>
       <c r="F169">
-        <v>2.764</v>
+        <v>2.22</v>
       </c>
       <c r="G169" t="s">
         <v>166</v>
@@ -4723,22 +4723,22 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46184</v>
+        <v>46226</v>
       </c>
       <c r="B170">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C170">
-        <v>677</v>
+        <v>421</v>
       </c>
       <c r="D170">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E170">
-        <v>15.1</v>
+        <v>38.5</v>
       </c>
       <c r="F170">
-        <v>2.679</v>
+        <v>1.772</v>
       </c>
       <c r="G170" t="s">
         <v>167</v>
